--- a/research/traditional_assets/database/data/kenya/kenya_power.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_power.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.109694304798309</v>
+        <v>0.109396721883914</v>
       </c>
       <c r="C2">
-        <v>1142.473918740793</v>
+        <v>1139.052990037665</v>
       </c>
       <c r="D2">
-        <v>1067.073918740793</v>
+        <v>1072.066990037664</v>
       </c>
       <c r="E2">
-        <v>-769</v>
+        <v>-760.586</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.414</v>
       </c>
       <c r="G2">
         <v>75.40000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4232241999999999</v>
       </c>
       <c r="N2">
-        <v>324.7734693877551</v>
+        <v>324.3502451877551</v>
       </c>
       <c r="O2">
-        <v>97.43204081632653</v>
+        <v>97.30507355632655</v>
       </c>
       <c r="P2">
-        <v>227.3414285714286</v>
+        <v>227.0451716314286</v>
       </c>
       <c r="Q2">
-        <v>351.2414285714286</v>
+        <v>350.9451716314286</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.109694304798309</v>
+        <v>0.1101460827110243</v>
       </c>
       <c r="T2">
-        <v>0.445499369788039</v>
+        <v>0.4486493653319948</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>767.3792504959669</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.109396721883914</v>
+        <v>0.1090991389695191</v>
       </c>
       <c r="C3">
-        <v>1139.052990037665</v>
+        <v>1135.679008346217</v>
       </c>
       <c r="D3">
-        <v>1072.066990037664</v>
+        <v>1077.107008346217</v>
       </c>
       <c r="E3">
-        <v>-760.586</v>
+        <v>-752.172</v>
       </c>
       <c r="F3">
-        <v>8.414</v>
+        <v>16.828</v>
       </c>
       <c r="G3">
         <v>75.40000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M3">
-        <v>0.4232241999999999</v>
+        <v>0.8464483999999999</v>
       </c>
       <c r="N3">
-        <v>324.3502451877551</v>
+        <v>323.9270209877552</v>
       </c>
       <c r="O3">
-        <v>97.30507355632655</v>
+        <v>97.17810629632655</v>
       </c>
       <c r="P3">
-        <v>227.0451716314286</v>
+        <v>226.7489146914286</v>
       </c>
       <c r="Q3">
-        <v>350.9451716314286</v>
+        <v>350.6489146914286</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1101460827110243</v>
+        <v>0.1106070805811419</v>
       </c>
       <c r="T3">
-        <v>0.4486493653319948</v>
+        <v>0.4518636464992967</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>767.3792504959669</v>
+        <v>383.6896252479835</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1090991389695191</v>
+        <v>0.1088015560551242</v>
       </c>
       <c r="C4">
-        <v>1135.679008346217</v>
+        <v>1132.352638918047</v>
       </c>
       <c r="D4">
-        <v>1077.107008346217</v>
+        <v>1082.194638918047</v>
       </c>
       <c r="E4">
-        <v>-752.172</v>
+        <v>-743.758</v>
       </c>
       <c r="F4">
-        <v>16.828</v>
+        <v>25.242</v>
       </c>
       <c r="G4">
         <v>75.40000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M4">
-        <v>0.8464483999999999</v>
+        <v>1.2696726</v>
       </c>
       <c r="N4">
-        <v>323.9270209877552</v>
+        <v>323.5037967877552</v>
       </c>
       <c r="O4">
-        <v>97.17810629632655</v>
+        <v>97.05113903632655</v>
       </c>
       <c r="P4">
-        <v>226.7489146914286</v>
+        <v>226.4526577514286</v>
       </c>
       <c r="Q4">
-        <v>350.6489146914286</v>
+        <v>350.3526577514286</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1106070805811419</v>
+        <v>0.1110775835619837</v>
       </c>
       <c r="T4">
-        <v>0.4518636464992967</v>
+        <v>0.4551442015050996</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>383.6896252479835</v>
+        <v>255.7930834986556</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1088015560551242</v>
+        <v>0.1085039731407293</v>
       </c>
       <c r="C5">
-        <v>1132.352638918047</v>
+        <v>1129.074559633454</v>
       </c>
       <c r="D5">
-        <v>1082.194638918047</v>
+        <v>1087.330559633454</v>
       </c>
       <c r="E5">
-        <v>-743.758</v>
+        <v>-735.3440000000001</v>
       </c>
       <c r="F5">
-        <v>25.242</v>
+        <v>33.656</v>
       </c>
       <c r="G5">
         <v>75.40000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M5">
-        <v>1.2696726</v>
+        <v>1.6928968</v>
       </c>
       <c r="N5">
-        <v>323.5037967877552</v>
+        <v>323.0805725877551</v>
       </c>
       <c r="O5">
-        <v>97.05113903632655</v>
+        <v>96.92417177632653</v>
       </c>
       <c r="P5">
-        <v>226.4526577514286</v>
+        <v>226.1564008114286</v>
       </c>
       <c r="Q5">
-        <v>350.3526577514286</v>
+        <v>350.0564008114285</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1110775835619837</v>
+        <v>0.1115578886882596</v>
       </c>
       <c r="T5">
-        <v>0.4551442015050996</v>
+        <v>0.4584931014068568</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>255.7930834986556</v>
+        <v>191.8448126239917</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1085039731407293</v>
+        <v>0.1082063902263343</v>
       </c>
       <c r="C6">
-        <v>1129.074559633454</v>
+        <v>1125.845461302544</v>
       </c>
       <c r="D6">
-        <v>1087.330559633454</v>
+        <v>1092.515461302544</v>
       </c>
       <c r="E6">
-        <v>-735.3440000000001</v>
+        <v>-726.9299999999999</v>
       </c>
       <c r="F6">
-        <v>33.656</v>
+        <v>42.07</v>
       </c>
       <c r="G6">
         <v>75.40000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M6">
-        <v>1.6928968</v>
+        <v>2.116121</v>
       </c>
       <c r="N6">
-        <v>323.0805725877551</v>
+        <v>322.6573483877551</v>
       </c>
       <c r="O6">
-        <v>96.92417177632653</v>
+        <v>96.79720451632653</v>
       </c>
       <c r="P6">
-        <v>226.1564008114286</v>
+        <v>225.8601438714286</v>
       </c>
       <c r="Q6">
-        <v>350.0564008114285</v>
+        <v>349.7601438714286</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1115578886882596</v>
+        <v>0.1120483055014045</v>
       </c>
       <c r="T6">
-        <v>0.4584931014068568</v>
+        <v>0.4619125044644404</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>191.8448126239917</v>
+        <v>153.4758500991934</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1082063902263343</v>
+        <v>0.1079088073119394</v>
       </c>
       <c r="C7">
-        <v>1125.845461302544</v>
+        <v>1122.666047974979</v>
       </c>
       <c r="D7">
-        <v>1092.515461302544</v>
+        <v>1097.750047974979</v>
       </c>
       <c r="E7">
-        <v>-726.9299999999999</v>
+        <v>-718.516</v>
       </c>
       <c r="F7">
-        <v>42.07</v>
+        <v>50.484</v>
       </c>
       <c r="G7">
         <v>75.40000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M7">
-        <v>2.116121</v>
+        <v>2.5393452</v>
       </c>
       <c r="N7">
-        <v>322.6573483877551</v>
+        <v>322.2341241877551</v>
       </c>
       <c r="O7">
-        <v>96.79720451632653</v>
+        <v>96.67023725632653</v>
       </c>
       <c r="P7">
-        <v>225.8601438714286</v>
+        <v>225.5638869314286</v>
       </c>
       <c r="Q7">
-        <v>349.7601438714286</v>
+        <v>349.4638869314286</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1120483055014045</v>
+        <v>0.1125491567148292</v>
       </c>
       <c r="T7">
-        <v>0.4619125044644404</v>
+        <v>0.4654046607785683</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>153.4758500991934</v>
+        <v>127.8965417493278</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1079088073119394</v>
+        <v>0.1076112243975445</v>
       </c>
       <c r="C8">
-        <v>1122.666047974979</v>
+        <v>1119.537037258681</v>
       </c>
       <c r="D8">
-        <v>1097.750047974979</v>
+        <v>1103.035037258681</v>
       </c>
       <c r="E8">
-        <v>-718.516</v>
+        <v>-710.102</v>
       </c>
       <c r="F8">
-        <v>50.48399999999999</v>
+        <v>58.89799999999999</v>
       </c>
       <c r="G8">
         <v>75.40000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M8">
-        <v>2.5393452</v>
+        <v>2.962569399999999</v>
       </c>
       <c r="N8">
-        <v>322.2341241877551</v>
+        <v>321.8108999877551</v>
       </c>
       <c r="O8">
-        <v>96.67023725632653</v>
+        <v>96.54326999632654</v>
       </c>
       <c r="P8">
-        <v>225.5638869314286</v>
+        <v>225.2676299914286</v>
       </c>
       <c r="Q8">
-        <v>349.4638869314286</v>
+        <v>349.1676299914286</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1125491567148292</v>
+        <v>0.1130607789220908</v>
       </c>
       <c r="T8">
-        <v>0.4654046607785683</v>
+        <v>0.4689719172284841</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>127.8965417493278</v>
+        <v>109.6256072137096</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1076112243975445</v>
+        <v>0.1073136414831496</v>
       </c>
       <c r="C9">
-        <v>1119.537037258681</v>
+        <v>1116.459160647785</v>
       </c>
       <c r="D9">
-        <v>1103.035037258681</v>
+        <v>1108.371160647784</v>
       </c>
       <c r="E9">
-        <v>-710.102</v>
+        <v>-701.688</v>
       </c>
       <c r="F9">
-        <v>58.898</v>
+        <v>67.312</v>
       </c>
       <c r="G9">
         <v>75.40000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M9">
-        <v>2.9625694</v>
+        <v>3.3857936</v>
       </c>
       <c r="N9">
-        <v>321.8108999877551</v>
+        <v>321.3876757877551</v>
       </c>
       <c r="O9">
-        <v>96.54326999632654</v>
+        <v>96.41630273632654</v>
       </c>
       <c r="P9">
-        <v>225.2676299914286</v>
+        <v>224.9713730514286</v>
       </c>
       <c r="Q9">
-        <v>349.1676299914286</v>
+        <v>348.8713730514286</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1130607789220908</v>
+        <v>0.1135835233512495</v>
       </c>
       <c r="T9">
-        <v>0.4689719172284841</v>
+        <v>0.4726167227316588</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>109.6256072137095</v>
+        <v>95.92240631199586</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1073136414831496</v>
+        <v>0.1070160585687546</v>
       </c>
       <c r="C10">
-        <v>1116.459160647785</v>
+        <v>1113.433163860151</v>
       </c>
       <c r="D10">
-        <v>1108.371160647784</v>
+        <v>1113.759163860151</v>
       </c>
       <c r="E10">
-        <v>-701.688</v>
+        <v>-693.274</v>
       </c>
       <c r="F10">
-        <v>67.312</v>
+        <v>75.726</v>
       </c>
       <c r="G10">
         <v>75.40000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M10">
-        <v>3.3857936</v>
+        <v>3.8090178</v>
       </c>
       <c r="N10">
-        <v>321.3876757877551</v>
+        <v>320.9644515877551</v>
       </c>
       <c r="O10">
-        <v>96.41630273632654</v>
+        <v>96.28933547632654</v>
       </c>
       <c r="P10">
-        <v>224.9713730514286</v>
+        <v>224.6751161114286</v>
       </c>
       <c r="Q10">
-        <v>348.8713730514286</v>
+        <v>348.5751161114286</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1135835233512495</v>
+        <v>0.1141177566689611</v>
       </c>
       <c r="T10">
-        <v>0.4726167227316588</v>
+        <v>0.4763416338502878</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>95.92240631199586</v>
+        <v>85.26436116621854</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1070160585687546</v>
+        <v>0.1067184756543597</v>
       </c>
       <c r="C11">
-        <v>1113.433163860151</v>
+        <v>1110.459807184781</v>
       </c>
       <c r="D11">
-        <v>1113.759163860151</v>
+        <v>1119.199807184781</v>
       </c>
       <c r="E11">
-        <v>-693.274</v>
+        <v>-684.86</v>
       </c>
       <c r="F11">
-        <v>75.726</v>
+        <v>84.13999999999999</v>
       </c>
       <c r="G11">
         <v>75.40000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M11">
-        <v>3.8090178</v>
+        <v>4.232241999999999</v>
       </c>
       <c r="N11">
-        <v>320.9644515877551</v>
+        <v>320.5412273877552</v>
       </c>
       <c r="O11">
-        <v>96.28933547632654</v>
+        <v>96.16236821632654</v>
       </c>
       <c r="P11">
-        <v>224.6751161114286</v>
+        <v>224.3788591714286</v>
       </c>
       <c r="Q11">
-        <v>348.5751161114286</v>
+        <v>348.2788591714286</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1141177566689611</v>
+        <v>0.1146638618381774</v>
       </c>
       <c r="T11">
-        <v>0.4763416338502878</v>
+        <v>0.4801493207715531</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>85.26436116621854</v>
+        <v>76.7379250495967</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1067184756543597</v>
+        <v>0.1064208927399648</v>
       </c>
       <c r="C12">
-        <v>1110.459807184781</v>
+        <v>1107.539865839459</v>
       </c>
       <c r="D12">
-        <v>1119.199807184781</v>
+        <v>1124.693865839459</v>
       </c>
       <c r="E12">
-        <v>-684.86</v>
+        <v>-676.446</v>
       </c>
       <c r="F12">
-        <v>84.14</v>
+        <v>92.554</v>
       </c>
       <c r="G12">
         <v>75.40000000000001</v>
@@ -2271,28 +2271,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M12">
-        <v>4.232241999999999</v>
+        <v>4.6554662</v>
       </c>
       <c r="N12">
-        <v>320.5412273877552</v>
+        <v>320.1180031877552</v>
       </c>
       <c r="O12">
-        <v>96.16236821632654</v>
+        <v>96.03540095632654</v>
       </c>
       <c r="P12">
-        <v>224.3788591714286</v>
+        <v>224.0826022314286</v>
       </c>
       <c r="Q12">
-        <v>348.2788591714286</v>
+        <v>347.9826022314286</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1146638618381774</v>
+        <v>0.1152222390336683</v>
       </c>
       <c r="T12">
-        <v>0.4801493207715531</v>
+        <v>0.4840425736910491</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>76.7379250495967</v>
+        <v>69.76175004508789</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1064208927399648</v>
+        <v>0.1061233098255698</v>
       </c>
       <c r="C13">
-        <v>1107.539865839459</v>
+        <v>1104.674130338977</v>
       </c>
       <c r="D13">
-        <v>1124.693865839459</v>
+        <v>1130.242130338976</v>
       </c>
       <c r="E13">
-        <v>-676.446</v>
+        <v>-668.032</v>
       </c>
       <c r="F13">
-        <v>92.554</v>
+        <v>100.968</v>
       </c>
       <c r="G13">
         <v>75.40000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M13">
-        <v>4.6554662</v>
+        <v>5.078690399999999</v>
       </c>
       <c r="N13">
-        <v>320.1180031877552</v>
+        <v>319.6947789877552</v>
       </c>
       <c r="O13">
-        <v>96.03540095632654</v>
+        <v>95.90843369632655</v>
       </c>
       <c r="P13">
-        <v>224.0826022314286</v>
+        <v>223.7863452914286</v>
       </c>
       <c r="Q13">
-        <v>347.9826022314286</v>
+        <v>347.6863452914286</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1152222390336683</v>
+        <v>0.1157933066199657</v>
       </c>
       <c r="T13">
-        <v>0.4840425736910491</v>
+        <v>0.4880243096314427</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>69.76175004508789</v>
+        <v>63.94827087466391</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1061233098255698</v>
+        <v>0.1058257269111749</v>
       </c>
       <c r="C14">
-        <v>1104.674130338977</v>
+        <v>1101.863406874318</v>
       </c>
       <c r="D14">
-        <v>1130.242130338976</v>
+        <v>1135.845406874318</v>
       </c>
       <c r="E14">
-        <v>-668.032</v>
+        <v>-659.6179999999999</v>
       </c>
       <c r="F14">
-        <v>100.968</v>
+        <v>109.382</v>
       </c>
       <c r="G14">
         <v>75.40000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M14">
-        <v>5.078690399999999</v>
+        <v>5.5019146</v>
       </c>
       <c r="N14">
-        <v>319.6947789877552</v>
+        <v>319.2715547877551</v>
       </c>
       <c r="O14">
-        <v>95.90843369632655</v>
+        <v>95.78146643632654</v>
       </c>
       <c r="P14">
-        <v>223.7863452914286</v>
+        <v>223.4900883514286</v>
       </c>
       <c r="Q14">
-        <v>347.6863452914286</v>
+        <v>347.3900883514286</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1157933066199657</v>
+        <v>0.1163775021967528</v>
       </c>
       <c r="T14">
-        <v>0.4880243096314427</v>
+        <v>0.4920975797313856</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>63.94827087466391</v>
+        <v>59.02917311507436</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1058257269111749</v>
+        <v>0.10552814399678</v>
       </c>
       <c r="C15">
-        <v>1101.863406874318</v>
+        <v>1099.108517703176</v>
       </c>
       <c r="D15">
-        <v>1135.845406874318</v>
+        <v>1141.504517703176</v>
       </c>
       <c r="E15">
-        <v>-659.6179999999999</v>
+        <v>-651.204</v>
       </c>
       <c r="F15">
-        <v>109.382</v>
+        <v>117.796</v>
       </c>
       <c r="G15">
         <v>75.40000000000001</v>
@@ -2517,28 +2517,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M15">
-        <v>5.5019146</v>
+        <v>5.9251388</v>
       </c>
       <c r="N15">
-        <v>319.2715547877551</v>
+        <v>318.8483305877551</v>
       </c>
       <c r="O15">
-        <v>95.78146643632654</v>
+        <v>95.65449917632654</v>
       </c>
       <c r="P15">
-        <v>223.4900883514286</v>
+        <v>223.1938314114286</v>
       </c>
       <c r="Q15">
-        <v>347.3900883514286</v>
+        <v>347.0938314114286</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1163775021967528</v>
+        <v>0.116975283717186</v>
       </c>
       <c r="T15">
-        <v>0.4920975797313856</v>
+        <v>0.496265577042955</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>59.02917311507436</v>
+        <v>54.81280360685476</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.10552814399678</v>
+        <v>0.105230561082385</v>
       </c>
       <c r="C16">
-        <v>1099.108517703176</v>
+        <v>1096.4103015522</v>
       </c>
       <c r="D16">
-        <v>1141.504517703176</v>
+        <v>1147.2203015522</v>
       </c>
       <c r="E16">
-        <v>-651.204</v>
+        <v>-642.79</v>
       </c>
       <c r="F16">
-        <v>117.796</v>
+        <v>126.21</v>
       </c>
       <c r="G16">
         <v>75.40000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M16">
-        <v>5.9251388</v>
+        <v>6.348363000000001</v>
       </c>
       <c r="N16">
-        <v>318.8483305877551</v>
+        <v>318.4251063877551</v>
       </c>
       <c r="O16">
-        <v>95.65449917632654</v>
+        <v>95.52753191632654</v>
       </c>
       <c r="P16">
-        <v>223.1938314114286</v>
+        <v>222.8975744714286</v>
       </c>
       <c r="Q16">
-        <v>347.0938314114286</v>
+        <v>346.7975744714286</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.116975283717186</v>
+        <v>0.1175871306851589</v>
       </c>
       <c r="T16">
-        <v>0.496265577042955</v>
+        <v>0.5005316448795026</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>54.81280360685476</v>
+        <v>51.15861669973111</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.105230561082385</v>
+        <v>0.1049329781679901</v>
       </c>
       <c r="C17">
-        <v>1096.4103015522</v>
+        <v>1093.769614031389</v>
       </c>
       <c r="D17">
-        <v>1147.2203015522</v>
+        <v>1152.993614031389</v>
       </c>
       <c r="E17">
-        <v>-642.79</v>
+        <v>-634.376</v>
       </c>
       <c r="F17">
-        <v>126.21</v>
+        <v>134.624</v>
       </c>
       <c r="G17">
         <v>75.40000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M17">
-        <v>6.348362999999999</v>
+        <v>6.771587199999999</v>
       </c>
       <c r="N17">
-        <v>318.4251063877551</v>
+        <v>318.0018821877551</v>
       </c>
       <c r="O17">
-        <v>95.52753191632654</v>
+        <v>95.40056465632654</v>
       </c>
       <c r="P17">
-        <v>222.8975744714286</v>
+        <v>222.6013175314286</v>
       </c>
       <c r="Q17">
-        <v>346.7975744714286</v>
+        <v>346.5013175314286</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1175871306851589</v>
+        <v>0.1182135454380835</v>
       </c>
       <c r="T17">
-        <v>0.5005316448795026</v>
+        <v>0.5048992857597775</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>51.15861669973113</v>
+        <v>47.96120315599793</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1049329781679901</v>
+        <v>0.1046353952535952</v>
       </c>
       <c r="C18">
-        <v>1093.769614031389</v>
+        <v>1091.18732806107</v>
       </c>
       <c r="D18">
-        <v>1152.993614031389</v>
+        <v>1158.82532806107</v>
       </c>
       <c r="E18">
-        <v>-634.376</v>
+        <v>-625.962</v>
       </c>
       <c r="F18">
-        <v>134.624</v>
+        <v>143.038</v>
       </c>
       <c r="G18">
         <v>75.40000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M18">
-        <v>6.771587199999999</v>
+        <v>7.1948114</v>
       </c>
       <c r="N18">
-        <v>318.0018821877551</v>
+        <v>317.5786579877552</v>
       </c>
       <c r="O18">
-        <v>95.40056465632654</v>
+        <v>95.27359739632654</v>
       </c>
       <c r="P18">
-        <v>222.6013175314286</v>
+        <v>222.3050605914286</v>
       </c>
       <c r="Q18">
-        <v>346.5013175314286</v>
+        <v>346.2050605914286</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1182135454380835</v>
+        <v>0.1188550545224039</v>
       </c>
       <c r="T18">
-        <v>0.5048992857597775</v>
+        <v>0.5093721709986133</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>47.96120315599793</v>
+        <v>45.13995591152746</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1046353952535952</v>
+        <v>0.1043378123392003</v>
       </c>
       <c r="C19">
-        <v>1091.18732806107</v>
+        <v>1088.664334311882</v>
       </c>
       <c r="D19">
-        <v>1158.82532806107</v>
+        <v>1164.716334311882</v>
       </c>
       <c r="E19">
-        <v>-625.962</v>
+        <v>-617.548</v>
       </c>
       <c r="F19">
-        <v>143.038</v>
+        <v>151.452</v>
       </c>
       <c r="G19">
         <v>75.40000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M19">
-        <v>7.1948114</v>
+        <v>7.618035600000001</v>
       </c>
       <c r="N19">
-        <v>317.5786579877552</v>
+        <v>317.1554337877552</v>
       </c>
       <c r="O19">
-        <v>95.27359739632654</v>
+        <v>95.14663013632655</v>
       </c>
       <c r="P19">
-        <v>222.3050605914286</v>
+        <v>222.0088036514286</v>
       </c>
       <c r="Q19">
-        <v>346.2050605914286</v>
+        <v>345.9088036514286</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1188550545224039</v>
+        <v>0.1195122101697564</v>
       </c>
       <c r="T19">
-        <v>0.5093721709986133</v>
+        <v>0.5139541509993718</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>45.13995591152746</v>
+        <v>42.63218058310926</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1043378123392003</v>
+        <v>0.1040402294248054</v>
       </c>
       <c r="C20">
-        <v>1088.664334311881</v>
+        <v>1086.201541658264</v>
       </c>
       <c r="D20">
-        <v>1164.716334311881</v>
+        <v>1170.667541658264</v>
       </c>
       <c r="E20">
-        <v>-617.548</v>
+        <v>-609.134</v>
       </c>
       <c r="F20">
-        <v>151.452</v>
+        <v>159.866</v>
       </c>
       <c r="G20">
         <v>75.40000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M20">
-        <v>7.6180356</v>
+        <v>8.041259799999999</v>
       </c>
       <c r="N20">
-        <v>317.1554337877552</v>
+        <v>316.7322095877552</v>
       </c>
       <c r="O20">
-        <v>95.14663013632655</v>
+        <v>95.01966287632655</v>
       </c>
       <c r="P20">
-        <v>222.0088036514286</v>
+        <v>221.7125467114286</v>
       </c>
       <c r="Q20">
-        <v>345.9088036514286</v>
+        <v>345.6125467114286</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1195122101697564</v>
+        <v>0.1201855918824757</v>
       </c>
       <c r="T20">
-        <v>0.5139541509993718</v>
+        <v>0.518649266308791</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>42.63218058310927</v>
+        <v>40.38838160505089</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1040402294248054</v>
+        <v>0.1037426465104104</v>
       </c>
       <c r="C21">
-        <v>1086.201541658264</v>
+        <v>1083.799877645914</v>
       </c>
       <c r="D21">
-        <v>1170.667541658264</v>
+        <v>1176.679877645914</v>
       </c>
       <c r="E21">
-        <v>-609.134</v>
+        <v>-600.72</v>
       </c>
       <c r="F21">
-        <v>159.866</v>
+        <v>168.28</v>
       </c>
       <c r="G21">
         <v>75.40000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M21">
-        <v>8.041259799999999</v>
+        <v>8.464483999999999</v>
       </c>
       <c r="N21">
-        <v>316.7322095877552</v>
+        <v>316.3089853877551</v>
       </c>
       <c r="O21">
-        <v>95.01966287632655</v>
+        <v>94.89269561632653</v>
       </c>
       <c r="P21">
-        <v>221.7125467114286</v>
+        <v>221.4162897714286</v>
       </c>
       <c r="Q21">
-        <v>345.6125467114286</v>
+        <v>345.3162897714286</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1201855918824757</v>
+        <v>0.120875808138013</v>
       </c>
       <c r="T21">
-        <v>0.518649266308791</v>
+        <v>0.5234617595009459</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>40.38838160505089</v>
+        <v>38.36896252479834</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1037426465104104</v>
+        <v>0.1034450635960155</v>
       </c>
       <c r="C22">
-        <v>1083.799877645914</v>
+        <v>1081.46028897372</v>
       </c>
       <c r="D22">
-        <v>1176.679877645914</v>
+        <v>1182.754288973719</v>
       </c>
       <c r="E22">
-        <v>-600.72</v>
+        <v>-592.306</v>
       </c>
       <c r="F22">
-        <v>168.28</v>
+        <v>176.694</v>
       </c>
       <c r="G22">
         <v>75.40000000000001</v>
@@ -3091,28 +3091,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M22">
-        <v>8.464483999999999</v>
+        <v>8.887708200000001</v>
       </c>
       <c r="N22">
-        <v>316.3089853877551</v>
+        <v>315.8857611877551</v>
       </c>
       <c r="O22">
-        <v>94.89269561632653</v>
+        <v>94.76572835632653</v>
       </c>
       <c r="P22">
-        <v>221.4162897714286</v>
+        <v>221.1200328314286</v>
       </c>
       <c r="Q22">
-        <v>345.3162897714286</v>
+        <v>345.0200328314286</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.120875808138013</v>
+        <v>0.1215834982228045</v>
       </c>
       <c r="T22">
-        <v>0.5234617595009459</v>
+        <v>0.5283960879637881</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>38.36896252479834</v>
+        <v>36.54186907123651</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1034450635960155</v>
+        <v>0.1031474806816206</v>
       </c>
       <c r="C23">
-        <v>1081.46028897372</v>
+        <v>1079.183741990705</v>
       </c>
       <c r="D23">
-        <v>1182.75428897372</v>
+        <v>1188.891741990705</v>
       </c>
       <c r="E23">
-        <v>-592.306</v>
+        <v>-583.8920000000001</v>
       </c>
       <c r="F23">
-        <v>176.694</v>
+        <v>185.108</v>
       </c>
       <c r="G23">
         <v>75.40000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M23">
-        <v>8.887708199999999</v>
+        <v>9.3109324</v>
       </c>
       <c r="N23">
-        <v>315.8857611877551</v>
+        <v>315.4625369877551</v>
       </c>
       <c r="O23">
-        <v>94.76572835632653</v>
+        <v>94.63876109632653</v>
       </c>
       <c r="P23">
-        <v>221.1200328314286</v>
+        <v>220.8237758914286</v>
       </c>
       <c r="Q23">
-        <v>345.0200328314286</v>
+        <v>344.7237758914285</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1215834982228044</v>
+        <v>0.1223093342072059</v>
       </c>
       <c r="T23">
-        <v>0.528396087963788</v>
+        <v>0.5334569376692672</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>36.54186907123652</v>
+        <v>34.88087502254394</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1031474806816206</v>
+        <v>0.1028498977672257</v>
       </c>
       <c r="C24">
-        <v>1079.183741990705</v>
+        <v>1076.971223208518</v>
       </c>
       <c r="D24">
-        <v>1188.891741990705</v>
+        <v>1195.093223208518</v>
       </c>
       <c r="E24">
-        <v>-583.8920000000001</v>
+        <v>-575.4780000000001</v>
       </c>
       <c r="F24">
-        <v>185.108</v>
+        <v>193.522</v>
       </c>
       <c r="G24">
         <v>75.40000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M24">
-        <v>9.3109324</v>
+        <v>9.734156599999999</v>
       </c>
       <c r="N24">
-        <v>315.4625369877551</v>
+        <v>315.0393127877551</v>
       </c>
       <c r="O24">
-        <v>94.63876109632653</v>
+        <v>94.51179383632653</v>
       </c>
       <c r="P24">
-        <v>220.8237758914286</v>
+        <v>220.5275189514286</v>
       </c>
       <c r="Q24">
-        <v>344.7237758914285</v>
+        <v>344.4275189514286</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1223093342072059</v>
+        <v>0.123054023074319</v>
       </c>
       <c r="T24">
-        <v>0.5334569376692672</v>
+        <v>0.5386492380164472</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>34.88087502254394</v>
+        <v>33.36431523895508</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1028498977672257</v>
+        <v>0.1025523148528307</v>
       </c>
       <c r="C25">
-        <v>1076.971223208518</v>
+        <v>1074.823739830057</v>
       </c>
       <c r="D25">
-        <v>1195.093223208518</v>
+        <v>1201.359739830056</v>
       </c>
       <c r="E25">
-        <v>-575.4780000000001</v>
+        <v>-567.064</v>
       </c>
       <c r="F25">
-        <v>193.522</v>
+        <v>201.936</v>
       </c>
       <c r="G25">
         <v>75.40000000000001</v>
@@ -3337,28 +3337,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M25">
-        <v>9.734156599999999</v>
+        <v>10.1573808</v>
       </c>
       <c r="N25">
-        <v>315.0393127877551</v>
+        <v>314.6160885877551</v>
       </c>
       <c r="O25">
-        <v>94.51179383632653</v>
+        <v>94.38482657632655</v>
       </c>
       <c r="P25">
-        <v>220.5275189514286</v>
+        <v>220.2312620114286</v>
       </c>
       <c r="Q25">
-        <v>344.4275189514286</v>
+        <v>344.1312620114286</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.123054023074319</v>
+        <v>0.1238183090168825</v>
       </c>
       <c r="T25">
-        <v>0.5386492380164472</v>
+        <v>0.5439781778464476</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>33.36431523895508</v>
+        <v>31.97413543733195</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1025523148528307</v>
+        <v>0.1022547319384358</v>
       </c>
       <c r="C26">
-        <v>1074.823739830057</v>
+        <v>1072.742320294795</v>
       </c>
       <c r="D26">
-        <v>1201.359739830056</v>
+        <v>1207.692320294795</v>
       </c>
       <c r="E26">
-        <v>-567.0640000000001</v>
+        <v>-558.65</v>
       </c>
       <c r="F26">
-        <v>201.936</v>
+        <v>210.35</v>
       </c>
       <c r="G26">
         <v>75.40000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M26">
-        <v>10.1573808</v>
+        <v>10.580605</v>
       </c>
       <c r="N26">
-        <v>314.6160885877551</v>
+        <v>314.1928643877552</v>
       </c>
       <c r="O26">
-        <v>94.38482657632655</v>
+        <v>94.25785931632655</v>
       </c>
       <c r="P26">
-        <v>220.2312620114286</v>
+        <v>219.9350050714286</v>
       </c>
       <c r="Q26">
-        <v>344.1312620114286</v>
+        <v>343.8350050714286</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1238183090168825</v>
+        <v>0.1246029759179144</v>
       </c>
       <c r="T26">
-        <v>0.5439781778464476</v>
+        <v>0.5494492227385814</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>31.97413543733195</v>
+        <v>30.69517001983868</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1022547319384358</v>
+        <v>0.1019571490240408</v>
       </c>
       <c r="C27">
-        <v>1072.742320294795</v>
+        <v>1070.728014841465</v>
       </c>
       <c r="D27">
-        <v>1207.692320294795</v>
+        <v>1214.092014841465</v>
       </c>
       <c r="E27">
-        <v>-558.65</v>
+        <v>-550.236</v>
       </c>
       <c r="F27">
-        <v>210.35</v>
+        <v>218.764</v>
       </c>
       <c r="G27">
         <v>75.40000000000001</v>
@@ -3501,28 +3501,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M27">
-        <v>10.580605</v>
+        <v>11.0038292</v>
       </c>
       <c r="N27">
-        <v>314.1928643877552</v>
+        <v>313.7696401877552</v>
       </c>
       <c r="O27">
-        <v>94.25785931632655</v>
+        <v>94.13089205632654</v>
       </c>
       <c r="P27">
-        <v>219.9350050714286</v>
+        <v>219.6387481314286</v>
       </c>
       <c r="Q27">
-        <v>343.8350050714286</v>
+        <v>343.5387481314286</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1246029759179144</v>
+        <v>0.1254088500324876</v>
       </c>
       <c r="T27">
-        <v>0.5494492227385814</v>
+        <v>0.555068133708881</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>30.69517001983868</v>
+        <v>29.51458655753719</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1019571490240408</v>
+        <v>0.1016595661096459</v>
       </c>
       <c r="C28">
-        <v>1070.728014841465</v>
+        <v>1068.781896088716</v>
       </c>
       <c r="D28">
-        <v>1214.092014841465</v>
+        <v>1220.559896088716</v>
       </c>
       <c r="E28">
-        <v>-550.236</v>
+        <v>-541.822</v>
       </c>
       <c r="F28">
-        <v>218.764</v>
+        <v>227.178</v>
       </c>
       <c r="G28">
         <v>75.40000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M28">
-        <v>11.0038292</v>
+        <v>11.4270534</v>
       </c>
       <c r="N28">
-        <v>313.7696401877552</v>
+        <v>313.3464159877552</v>
       </c>
       <c r="O28">
-        <v>94.13089205632654</v>
+        <v>94.00392479632654</v>
       </c>
       <c r="P28">
-        <v>219.6387481314286</v>
+        <v>219.3424911914286</v>
       </c>
       <c r="Q28">
-        <v>343.5387481314286</v>
+        <v>343.2424911914286</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1254088500324876</v>
+        <v>0.1262368028899259</v>
       </c>
       <c r="T28">
-        <v>0.555068133708881</v>
+        <v>0.5608409874454903</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>29.51458655753719</v>
+        <v>28.42145372207284</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1016595661096459</v>
+        <v>0.101361983195251</v>
       </c>
       <c r="C29">
-        <v>1068.781896088716</v>
+        <v>1066.905059634431</v>
       </c>
       <c r="D29">
-        <v>1220.559896088716</v>
+        <v>1227.097059634431</v>
       </c>
       <c r="E29">
-        <v>-541.822</v>
+        <v>-533.408</v>
       </c>
       <c r="F29">
-        <v>227.178</v>
+        <v>235.592</v>
       </c>
       <c r="G29">
         <v>75.40000000000001</v>
@@ -3665,28 +3665,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M29">
-        <v>11.4270534</v>
+        <v>11.8502776</v>
       </c>
       <c r="N29">
-        <v>313.3464159877552</v>
+        <v>312.9231917877551</v>
       </c>
       <c r="O29">
-        <v>94.00392479632654</v>
+        <v>93.87695753632653</v>
       </c>
       <c r="P29">
-        <v>219.3424911914286</v>
+        <v>219.0462342514286</v>
       </c>
       <c r="Q29">
-        <v>343.2424911914286</v>
+        <v>342.9462342514286</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1262368028899259</v>
+        <v>0.1270877544378486</v>
       </c>
       <c r="T29">
-        <v>0.5608409874454903</v>
+        <v>0.5667741982303385</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>28.42145372207284</v>
+        <v>27.40640180342738</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.101361983195251</v>
+        <v>0.1010644002808561</v>
       </c>
       <c r="C30">
-        <v>1066.905059634431</v>
+        <v>1065.098624674415</v>
       </c>
       <c r="D30">
-        <v>1227.097059634431</v>
+        <v>1233.704624674415</v>
       </c>
       <c r="E30">
-        <v>-533.408</v>
+        <v>-524.9939999999999</v>
       </c>
       <c r="F30">
-        <v>235.592</v>
+        <v>244.006</v>
       </c>
       <c r="G30">
         <v>75.40000000000001</v>
@@ -3747,28 +3747,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M30">
-        <v>11.8502776</v>
+        <v>12.2735018</v>
       </c>
       <c r="N30">
-        <v>312.9231917877551</v>
+        <v>312.4999675877551</v>
       </c>
       <c r="O30">
-        <v>93.87695753632653</v>
+        <v>93.74999027632653</v>
       </c>
       <c r="P30">
-        <v>219.0462342514286</v>
+        <v>218.7499773114286</v>
       </c>
       <c r="Q30">
-        <v>342.9462342514286</v>
+        <v>342.6499773114286</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1270877544378486</v>
+        <v>0.12796267645191</v>
       </c>
       <c r="T30">
-        <v>0.5667741982303385</v>
+        <v>0.5728745417133516</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>27.40640180342738</v>
+        <v>26.46135346537816</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1010644002808561</v>
+        <v>0.1007668173664612</v>
       </c>
       <c r="C31">
-        <v>1065.098624674415</v>
+        <v>1063.363734641169</v>
       </c>
       <c r="D31">
-        <v>1233.704624674415</v>
+        <v>1240.383734641169</v>
       </c>
       <c r="E31">
-        <v>-524.994</v>
+        <v>-516.58</v>
       </c>
       <c r="F31">
-        <v>244.006</v>
+        <v>252.42</v>
       </c>
       <c r="G31">
         <v>75.40000000000001</v>
@@ -3829,28 +3829,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M31">
-        <v>12.2735018</v>
+        <v>12.696726</v>
       </c>
       <c r="N31">
-        <v>312.4999675877551</v>
+        <v>312.0767433877551</v>
       </c>
       <c r="O31">
-        <v>93.74999027632653</v>
+        <v>93.62302301632654</v>
       </c>
       <c r="P31">
-        <v>218.7499773114286</v>
+        <v>218.4537203714286</v>
       </c>
       <c r="Q31">
-        <v>342.6499773114286</v>
+        <v>342.3537203714286</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.12796267645191</v>
+        <v>0.1288625962378017</v>
       </c>
       <c r="T31">
-        <v>0.5728745417133516</v>
+        <v>0.5791491807244508</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>26.46135346537817</v>
+        <v>25.57930834986556</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1007668173664612</v>
+        <v>0.1004692344520662</v>
       </c>
       <c r="C32">
-        <v>1063.363734641169</v>
+        <v>1061.701557863538</v>
       </c>
       <c r="D32">
-        <v>1240.383734641169</v>
+        <v>1247.135557863538</v>
       </c>
       <c r="E32">
-        <v>-516.58</v>
+        <v>-508.166</v>
       </c>
       <c r="F32">
-        <v>252.42</v>
+        <v>260.834</v>
       </c>
       <c r="G32">
         <v>75.40000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M32">
-        <v>12.696726</v>
+        <v>13.1199502</v>
       </c>
       <c r="N32">
-        <v>312.0767433877551</v>
+        <v>311.6535191877551</v>
       </c>
       <c r="O32">
-        <v>93.62302301632654</v>
+        <v>93.49605575632654</v>
       </c>
       <c r="P32">
-        <v>218.4537203714286</v>
+        <v>218.1574634314286</v>
       </c>
       <c r="Q32">
-        <v>342.3537203714286</v>
+        <v>342.0574634314286</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1288625962378017</v>
+        <v>0.1297886006551685</v>
       </c>
       <c r="T32">
-        <v>0.5791491807244508</v>
+        <v>0.5856056933300744</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>25.57930834986556</v>
+        <v>24.75416937083764</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1004692344520662</v>
+        <v>0.1001716515376713</v>
       </c>
       <c r="C33">
-        <v>1061.701557863538</v>
+        <v>1060.11328824801</v>
       </c>
       <c r="D33">
-        <v>1247.135557863538</v>
+        <v>1253.96128824801</v>
       </c>
       <c r="E33">
-        <v>-508.166</v>
+        <v>-499.752</v>
       </c>
       <c r="F33">
-        <v>260.834</v>
+        <v>269.248</v>
       </c>
       <c r="G33">
         <v>75.40000000000001</v>
@@ -3993,28 +3993,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M33">
-        <v>13.1199502</v>
+        <v>13.5431744</v>
       </c>
       <c r="N33">
-        <v>311.6535191877551</v>
+        <v>311.2302949877551</v>
       </c>
       <c r="O33">
-        <v>93.49605575632654</v>
+        <v>93.36908849632654</v>
       </c>
       <c r="P33">
-        <v>218.1574634314286</v>
+        <v>217.8612064914286</v>
       </c>
       <c r="Q33">
-        <v>342.0574634314286</v>
+        <v>341.7612064914286</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1297886006551685</v>
+        <v>0.1307418404965754</v>
       </c>
       <c r="T33">
-        <v>0.5856056933300744</v>
+        <v>0.5922521033652753</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>24.75416937083764</v>
+        <v>23.98060157799896</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1001716515376713</v>
+        <v>0.09987406862327637</v>
       </c>
       <c r="C34">
-        <v>1060.11328824801</v>
+        <v>1058.600145982518</v>
       </c>
       <c r="D34">
-        <v>1253.96128824801</v>
+        <v>1260.862145982518</v>
       </c>
       <c r="E34">
-        <v>-499.752</v>
+        <v>-491.338</v>
       </c>
       <c r="F34">
-        <v>269.248</v>
+        <v>277.662</v>
       </c>
       <c r="G34">
         <v>75.40000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M34">
-        <v>13.5431744</v>
+        <v>13.9663986</v>
       </c>
       <c r="N34">
-        <v>311.2302949877551</v>
+        <v>310.8070707877552</v>
       </c>
       <c r="O34">
-        <v>93.36908849632654</v>
+        <v>93.24212123632654</v>
       </c>
       <c r="P34">
-        <v>217.8612064914286</v>
+        <v>217.5649495514286</v>
       </c>
       <c r="Q34">
-        <v>341.7612064914286</v>
+        <v>341.4649495514286</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1307418404965754</v>
+        <v>0.1317235352586215</v>
       </c>
       <c r="T34">
-        <v>0.5922521033652753</v>
+        <v>0.5990969137000346</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>23.98060157799896</v>
+        <v>23.25391668169597</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09987406862327637</v>
+        <v>0.09957648570888145</v>
       </c>
       <c r="C35">
-        <v>1058.600145982518</v>
+        <v>1057.16337826361</v>
       </c>
       <c r="D35">
-        <v>1260.862145982518</v>
+        <v>1267.83937826361</v>
       </c>
       <c r="E35">
-        <v>-491.338</v>
+        <v>-482.924</v>
       </c>
       <c r="F35">
-        <v>277.662</v>
+        <v>286.076</v>
       </c>
       <c r="G35">
         <v>75.40000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M35">
-        <v>13.9663986</v>
+        <v>14.3896228</v>
       </c>
       <c r="N35">
-        <v>310.8070707877552</v>
+        <v>310.3838465877552</v>
       </c>
       <c r="O35">
-        <v>93.24212123632654</v>
+        <v>93.11515397632654</v>
       </c>
       <c r="P35">
-        <v>217.5649495514286</v>
+        <v>217.2686926114286</v>
       </c>
       <c r="Q35">
-        <v>341.4649495514286</v>
+        <v>341.1686926114286</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1317235352586215</v>
+        <v>0.1327349783467901</v>
       </c>
       <c r="T35">
-        <v>0.5990969137000346</v>
+        <v>0.6061491425297864</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>23.25391668169597</v>
+        <v>22.56997795576373</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09957648570888145</v>
+        <v>0.09927890279448651</v>
       </c>
       <c r="C36">
-        <v>1057.16337826361</v>
+        <v>1055.804260047895</v>
       </c>
       <c r="D36">
-        <v>1267.83937826361</v>
+        <v>1274.894260047895</v>
       </c>
       <c r="E36">
-        <v>-482.924</v>
+        <v>-474.51</v>
       </c>
       <c r="F36">
-        <v>286.076</v>
+        <v>294.49</v>
       </c>
       <c r="G36">
         <v>75.40000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M36">
-        <v>14.3896228</v>
+        <v>14.812847</v>
       </c>
       <c r="N36">
-        <v>310.3838465877552</v>
+        <v>309.9606223877552</v>
       </c>
       <c r="O36">
-        <v>93.11515397632654</v>
+        <v>92.98818671632655</v>
       </c>
       <c r="P36">
-        <v>217.2686926114286</v>
+        <v>216.9724356714286</v>
       </c>
       <c r="Q36">
-        <v>341.1686926114286</v>
+        <v>340.8724356714286</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1327349783467901</v>
+        <v>0.1337775427607485</v>
       </c>
       <c r="T36">
-        <v>0.6061491425297864</v>
+        <v>0.6134183630158383</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>22.56997795576373</v>
+        <v>21.92512144274191</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09927890279448651</v>
+        <v>0.09898131988009158</v>
       </c>
       <c r="C37">
-        <v>1055.804260047895</v>
+        <v>1054.524094828713</v>
       </c>
       <c r="D37">
-        <v>1274.894260047895</v>
+        <v>1282.028094828713</v>
       </c>
       <c r="E37">
-        <v>-474.51</v>
+        <v>-466.0959999999999</v>
       </c>
       <c r="F37">
-        <v>294.49</v>
+        <v>302.9040000000001</v>
       </c>
       <c r="G37">
         <v>75.40000000000001</v>
@@ -4321,28 +4321,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M37">
-        <v>14.812847</v>
+        <v>15.2360712</v>
       </c>
       <c r="N37">
-        <v>309.9606223877552</v>
+        <v>309.5373981877551</v>
       </c>
       <c r="O37">
-        <v>92.98818671632655</v>
+        <v>92.86121945632654</v>
       </c>
       <c r="P37">
-        <v>216.9724356714286</v>
+        <v>216.6761787314286</v>
       </c>
       <c r="Q37">
-        <v>340.8724356714286</v>
+        <v>340.5761787314286</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1337775427607485</v>
+        <v>0.1348526873126431</v>
       </c>
       <c r="T37">
-        <v>0.6134183630158383</v>
+        <v>0.6209147466420794</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>21.92512144274191</v>
+        <v>21.31609029155463</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09898131988009159</v>
+        <v>0.09868373696569668</v>
       </c>
       <c r="C38">
-        <v>1054.524094828713</v>
+        <v>1053.324215439039</v>
       </c>
       <c r="D38">
-        <v>1282.028094828713</v>
+        <v>1289.242215439039</v>
       </c>
       <c r="E38">
-        <v>-466.096</v>
+        <v>-457.682</v>
       </c>
       <c r="F38">
-        <v>302.904</v>
+        <v>311.318</v>
       </c>
       <c r="G38">
         <v>75.40000000000001</v>
@@ -4403,28 +4403,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M38">
-        <v>15.2360712</v>
+        <v>15.6592954</v>
       </c>
       <c r="N38">
-        <v>309.5373981877551</v>
+        <v>309.1141739877551</v>
       </c>
       <c r="O38">
-        <v>92.86121945632654</v>
+        <v>92.73425219632654</v>
       </c>
       <c r="P38">
-        <v>216.6761787314286</v>
+        <v>216.3799217914286</v>
       </c>
       <c r="Q38">
-        <v>340.5761787314286</v>
+        <v>340.2799217914286</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1348526873126431</v>
+        <v>0.1359619634376138</v>
       </c>
       <c r="T38">
-        <v>0.6209147466420794</v>
+        <v>0.6286491107008995</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>21.31609029155463</v>
+        <v>20.73997974313424</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09868373696569668</v>
+        <v>0.09838615405130174</v>
       </c>
       <c r="C39">
-        <v>1053.324215439039</v>
+        <v>1052.205984881639</v>
       </c>
       <c r="D39">
-        <v>1289.242215439039</v>
+        <v>1296.537984881639</v>
       </c>
       <c r="E39">
-        <v>-457.682</v>
+        <v>-449.268</v>
       </c>
       <c r="F39">
-        <v>311.318</v>
+        <v>319.732</v>
       </c>
       <c r="G39">
         <v>75.40000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M39">
-        <v>15.6592954</v>
+        <v>16.0825196</v>
       </c>
       <c r="N39">
-        <v>309.1141739877551</v>
+        <v>308.6909497877551</v>
       </c>
       <c r="O39">
-        <v>92.73425219632654</v>
+        <v>92.60728493632654</v>
       </c>
       <c r="P39">
-        <v>216.3799217914286</v>
+        <v>216.0836648514286</v>
       </c>
       <c r="Q39">
-        <v>340.2799217914286</v>
+        <v>339.9836648514286</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1359619634376138</v>
+        <v>0.1371070226633899</v>
       </c>
       <c r="T39">
-        <v>0.6286491107008995</v>
+        <v>0.6366329703745203</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>20.73997974313424</v>
+        <v>20.19419080252544</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09838615405130174</v>
+        <v>0.09808857113690682</v>
       </c>
       <c r="C40">
-        <v>1052.205984881639</v>
+        <v>1051.170797187574</v>
       </c>
       <c r="D40">
-        <v>1296.537984881639</v>
+        <v>1303.916797187574</v>
       </c>
       <c r="E40">
-        <v>-449.268</v>
+        <v>-440.854</v>
       </c>
       <c r="F40">
-        <v>319.732</v>
+        <v>328.146</v>
       </c>
       <c r="G40">
         <v>75.40000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M40">
-        <v>16.0825196</v>
+        <v>16.5057438</v>
       </c>
       <c r="N40">
-        <v>308.6909497877551</v>
+        <v>308.2677255877551</v>
       </c>
       <c r="O40">
-        <v>92.60728493632654</v>
+        <v>92.48031767632654</v>
       </c>
       <c r="P40">
-        <v>216.0836648514286</v>
+        <v>215.7874079114286</v>
       </c>
       <c r="Q40">
-        <v>339.9836648514286</v>
+        <v>339.6874079114286</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1371070226633899</v>
+        <v>0.1382896248146013</v>
       </c>
       <c r="T40">
-        <v>0.6366329703745203</v>
+        <v>0.6448785959390794</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>20.19419080252544</v>
+        <v>19.67639103835812</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09808857113690682</v>
+        <v>0.09779098822251189</v>
       </c>
       <c r="C41">
-        <v>1051.170797187574</v>
+        <v>1050.220078304196</v>
       </c>
       <c r="D41">
-        <v>1303.916797187574</v>
+        <v>1311.380078304196</v>
       </c>
       <c r="E41">
-        <v>-440.854</v>
+        <v>-432.44</v>
       </c>
       <c r="F41">
-        <v>328.146</v>
+        <v>336.56</v>
       </c>
       <c r="G41">
         <v>75.40000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M41">
-        <v>16.5057438</v>
+        <v>16.928968</v>
       </c>
       <c r="N41">
-        <v>308.2677255877551</v>
+        <v>307.8445013877551</v>
       </c>
       <c r="O41">
-        <v>92.48031767632654</v>
+        <v>92.35335041632653</v>
       </c>
       <c r="P41">
-        <v>215.7874079114286</v>
+        <v>215.4911509714286</v>
       </c>
       <c r="Q41">
-        <v>339.6874079114286</v>
+        <v>339.3911509714286</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1382896248146013</v>
+        <v>0.1395116470375198</v>
       </c>
       <c r="T41">
-        <v>0.6448785959390794</v>
+        <v>0.6533990756891239</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>19.67639103835812</v>
+        <v>19.18448126239917</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09779098822251189</v>
+        <v>0.09749340530811695</v>
       </c>
       <c r="C42">
-        <v>1050.220078304196</v>
+        <v>1049.355287013802</v>
       </c>
       <c r="D42">
-        <v>1311.380078304196</v>
+        <v>1318.929287013802</v>
       </c>
       <c r="E42">
-        <v>-432.44</v>
+        <v>-424.026</v>
       </c>
       <c r="F42">
-        <v>336.56</v>
+        <v>344.974</v>
       </c>
       <c r="G42">
         <v>75.40000000000001</v>
@@ -4731,28 +4731,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M42">
-        <v>16.928968</v>
+        <v>17.3521922</v>
       </c>
       <c r="N42">
-        <v>307.8445013877551</v>
+        <v>307.4212771877552</v>
       </c>
       <c r="O42">
-        <v>92.35335041632653</v>
+        <v>92.22638315632655</v>
       </c>
       <c r="P42">
-        <v>215.4911509714286</v>
+        <v>215.1948940314286</v>
       </c>
       <c r="Q42">
-        <v>339.3911509714286</v>
+        <v>339.0948940314286</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1395116470375198</v>
+        <v>0.1407750937425711</v>
       </c>
       <c r="T42">
-        <v>0.6533990756891239</v>
+        <v>0.6622083852612037</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>19.18448126239917</v>
+        <v>18.71656708526749</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09749340530811695</v>
+        <v>0.09719582239372204</v>
       </c>
       <c r="C43">
-        <v>1049.355287013802</v>
+        <v>1048.577915884212</v>
       </c>
       <c r="D43">
-        <v>1318.929287013802</v>
+        <v>1326.565915884212</v>
       </c>
       <c r="E43">
-        <v>-424.026</v>
+        <v>-415.612</v>
       </c>
       <c r="F43">
-        <v>344.974</v>
+        <v>353.388</v>
       </c>
       <c r="G43">
         <v>75.40000000000001</v>
@@ -4813,28 +4813,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M43">
-        <v>17.3521922</v>
+        <v>17.7754164</v>
       </c>
       <c r="N43">
-        <v>307.4212771877552</v>
+        <v>306.9980529877552</v>
       </c>
       <c r="O43">
-        <v>92.22638315632655</v>
+        <v>92.09941589632655</v>
       </c>
       <c r="P43">
-        <v>215.1948940314286</v>
+        <v>214.8986370914286</v>
       </c>
       <c r="Q43">
-        <v>339.0948940314286</v>
+        <v>338.7986370914286</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1407750937425711</v>
+        <v>0.1420821075753828</v>
       </c>
       <c r="T43">
-        <v>0.6622083852612037</v>
+        <v>0.6713214641288726</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>18.71656708526749</v>
+        <v>18.27093453561826</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09719582239372204</v>
+        <v>0.09689823947932712</v>
       </c>
       <c r="C44">
-        <v>1048.577915884212</v>
+        <v>1047.889492252563</v>
       </c>
       <c r="D44">
-        <v>1326.565915884212</v>
+        <v>1334.291492252562</v>
       </c>
       <c r="E44">
-        <v>-415.612</v>
+        <v>-407.198</v>
       </c>
       <c r="F44">
-        <v>353.388</v>
+        <v>361.802</v>
       </c>
       <c r="G44">
         <v>75.40000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M44">
-        <v>17.7754164</v>
+        <v>18.1986406</v>
       </c>
       <c r="N44">
-        <v>306.9980529877552</v>
+        <v>306.5748287877552</v>
       </c>
       <c r="O44">
-        <v>92.09941589632655</v>
+        <v>91.97244863632655</v>
       </c>
       <c r="P44">
-        <v>214.8986370914286</v>
+        <v>214.6023801514286</v>
       </c>
       <c r="Q44">
-        <v>338.7986370914286</v>
+        <v>338.5023801514286</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1420821075753828</v>
+        <v>0.1434349815426791</v>
       </c>
       <c r="T44">
-        <v>0.6713214641288725</v>
+        <v>0.6807543001497929</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>18.27093453561826</v>
+        <v>17.84602908130156</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09689823947932712</v>
+        <v>0.09660065656493219</v>
       </c>
       <c r="C45">
-        <v>1047.889492252563</v>
+        <v>1047.29157924367</v>
       </c>
       <c r="D45">
-        <v>1334.291492252562</v>
+        <v>1342.10757924367</v>
       </c>
       <c r="E45">
-        <v>-407.198</v>
+        <v>-398.784</v>
       </c>
       <c r="F45">
-        <v>361.802</v>
+        <v>370.216</v>
       </c>
       <c r="G45">
         <v>75.40000000000001</v>
@@ -4977,28 +4977,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M45">
-        <v>18.1986406</v>
+        <v>18.6218648</v>
       </c>
       <c r="N45">
-        <v>306.5748287877552</v>
+        <v>306.1516045877551</v>
       </c>
       <c r="O45">
-        <v>91.97244863632655</v>
+        <v>91.84548137632653</v>
       </c>
       <c r="P45">
-        <v>214.6023801514286</v>
+        <v>214.3061232114286</v>
       </c>
       <c r="Q45">
-        <v>338.5023801514286</v>
+        <v>338.2061232114286</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1434349815426791</v>
+        <v>0.1448361724373789</v>
       </c>
       <c r="T45">
-        <v>0.6807543001497929</v>
+        <v>0.6905240231714603</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>17.84602908130156</v>
+        <v>17.44043751127197</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09660065656493219</v>
+        <v>0.09630307365053727</v>
       </c>
       <c r="C46">
-        <v>1047.29157924367</v>
+        <v>1046.785776824405</v>
       </c>
       <c r="D46">
-        <v>1342.10757924367</v>
+        <v>1350.015776824405</v>
       </c>
       <c r="E46">
-        <v>-398.784</v>
+        <v>-390.37</v>
       </c>
       <c r="F46">
-        <v>370.216</v>
+        <v>378.63</v>
       </c>
       <c r="G46">
         <v>75.40000000000001</v>
@@ -5059,28 +5059,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M46">
-        <v>18.6218648</v>
+        <v>19.045089</v>
       </c>
       <c r="N46">
-        <v>306.1516045877551</v>
+        <v>305.7283803877551</v>
       </c>
       <c r="O46">
-        <v>91.84548137632653</v>
+        <v>91.71851411632653</v>
       </c>
       <c r="P46">
-        <v>214.3061232114286</v>
+        <v>214.0098662714286</v>
       </c>
       <c r="Q46">
-        <v>338.2061232114286</v>
+        <v>337.9098662714285</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1448361724373789</v>
+        <v>0.1462883157282496</v>
       </c>
       <c r="T46">
-        <v>0.6905240231714603</v>
+        <v>0.7006490088484614</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>17.44043751127197</v>
+        <v>17.05287223324371</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09630307365053727</v>
+        <v>0.09600549073614234</v>
       </c>
       <c r="C47">
-        <v>1046.785776824405</v>
+        <v>1046.373722895561</v>
       </c>
       <c r="D47">
-        <v>1350.015776824405</v>
+        <v>1358.017722895561</v>
       </c>
       <c r="E47">
-        <v>-390.37</v>
+        <v>-381.956</v>
       </c>
       <c r="F47">
-        <v>378.63</v>
+        <v>387.044</v>
       </c>
       <c r="G47">
         <v>75.40000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M47">
-        <v>19.045089</v>
+        <v>19.4683132</v>
       </c>
       <c r="N47">
-        <v>305.7283803877551</v>
+        <v>305.3051561877551</v>
       </c>
       <c r="O47">
-        <v>91.71851411632653</v>
+        <v>91.59154685632653</v>
       </c>
       <c r="P47">
-        <v>214.0098662714286</v>
+        <v>213.7136093314286</v>
       </c>
       <c r="Q47">
-        <v>337.9098662714285</v>
+        <v>337.6136093314286</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1462883157282496</v>
+        <v>0.1477942421039673</v>
       </c>
       <c r="T47">
-        <v>0.7006490088484614</v>
+        <v>0.7111489939949807</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>17.05287223324371</v>
+        <v>16.68215761947754</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09600549073614234</v>
+        <v>0.0957079078217474</v>
       </c>
       <c r="C48">
-        <v>1046.373722895561</v>
+        <v>1046.057094422787</v>
       </c>
       <c r="D48">
-        <v>1358.017722895561</v>
+        <v>1366.115094422787</v>
       </c>
       <c r="E48">
-        <v>-381.956</v>
+        <v>-373.542</v>
       </c>
       <c r="F48">
-        <v>387.044</v>
+        <v>395.458</v>
       </c>
       <c r="G48">
         <v>75.40000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M48">
-        <v>19.4683132</v>
+        <v>19.8915374</v>
       </c>
       <c r="N48">
-        <v>305.3051561877551</v>
+        <v>304.8819319877551</v>
       </c>
       <c r="O48">
-        <v>91.59154685632653</v>
+        <v>91.46457959632654</v>
       </c>
       <c r="P48">
-        <v>213.7136093314286</v>
+        <v>213.4173523914286</v>
       </c>
       <c r="Q48">
-        <v>337.6136093314286</v>
+        <v>337.3173523914286</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1477942421039673</v>
+        <v>0.1493569958900894</v>
       </c>
       <c r="T48">
-        <v>0.7111489939949807</v>
+        <v>0.7220452049960858</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>16.68215761947754</v>
+        <v>16.32721809565886</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0957079078217474</v>
+        <v>0.09541032490735246</v>
       </c>
       <c r="C49">
-        <v>1046.057094422787</v>
+        <v>1045.83760860822</v>
       </c>
       <c r="D49">
-        <v>1366.115094422787</v>
+        <v>1374.30960860822</v>
       </c>
       <c r="E49">
-        <v>-373.542</v>
+        <v>-365.128</v>
       </c>
       <c r="F49">
-        <v>395.458</v>
+        <v>403.872</v>
       </c>
       <c r="G49">
         <v>75.40000000000001</v>
@@ -5305,28 +5305,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M49">
-        <v>19.8915374</v>
+        <v>20.3147616</v>
       </c>
       <c r="N49">
-        <v>304.8819319877551</v>
+        <v>304.4587077877551</v>
       </c>
       <c r="O49">
-        <v>91.46457959632654</v>
+        <v>91.33761233632654</v>
       </c>
       <c r="P49">
-        <v>213.4173523914286</v>
+        <v>213.1210954514286</v>
       </c>
       <c r="Q49">
-        <v>337.3173523914286</v>
+        <v>337.0210954514286</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1493569958900894</v>
+        <v>0.1509798555910624</v>
       </c>
       <c r="T49">
-        <v>0.7220452049960858</v>
+        <v>0.7333605010356949</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>16.32721809565886</v>
+        <v>15.98706771866597</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09541032490735246</v>
+        <v>0.09511274199295755</v>
       </c>
       <c r="C50">
-        <v>1045.83760860822</v>
+        <v>1045.717024104543</v>
       </c>
       <c r="D50">
-        <v>1374.30960860822</v>
+        <v>1382.603024104543</v>
       </c>
       <c r="E50">
-        <v>-365.128</v>
+        <v>-356.714</v>
       </c>
       <c r="F50">
-        <v>403.872</v>
+        <v>412.286</v>
       </c>
       <c r="G50">
         <v>75.40000000000001</v>
@@ -5387,28 +5387,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M50">
-        <v>20.3147616</v>
+        <v>20.7379858</v>
       </c>
       <c r="N50">
-        <v>304.4587077877551</v>
+        <v>304.0354835877552</v>
       </c>
       <c r="O50">
-        <v>91.33761233632654</v>
+        <v>91.21064507632654</v>
       </c>
       <c r="P50">
-        <v>213.1210954514286</v>
+        <v>212.8248385114286</v>
       </c>
       <c r="Q50">
-        <v>337.0210954514286</v>
+        <v>336.7248385114286</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1509798555910624</v>
+        <v>0.1526663568489364</v>
       </c>
       <c r="T50">
-        <v>0.7333605010356949</v>
+        <v>0.7451195341748965</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>15.98706771866598</v>
+        <v>15.66080103052993</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09511274199295755</v>
+        <v>0.09481515907856262</v>
       </c>
       <c r="C51">
-        <v>1045.717024104543</v>
+        <v>1045.697142273267</v>
       </c>
       <c r="D51">
-        <v>1382.603024104543</v>
+        <v>1390.997142273267</v>
       </c>
       <c r="E51">
-        <v>-356.714</v>
+        <v>-348.3</v>
       </c>
       <c r="F51">
-        <v>412.286</v>
+        <v>420.7</v>
       </c>
       <c r="G51">
         <v>75.40000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M51">
-        <v>20.7379858</v>
+        <v>21.16121</v>
       </c>
       <c r="N51">
-        <v>304.0354835877552</v>
+        <v>303.6122593877552</v>
       </c>
       <c r="O51">
-        <v>91.21064507632654</v>
+        <v>91.08367781632654</v>
       </c>
       <c r="P51">
-        <v>212.8248385114286</v>
+        <v>212.5285815714286</v>
       </c>
       <c r="Q51">
-        <v>336.7248385114286</v>
+        <v>336.4285815714286</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1526663568489364</v>
+        <v>0.1544203181571253</v>
       </c>
       <c r="T51">
-        <v>0.7451195341748965</v>
+        <v>0.7573489286396663</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>15.66080103052993</v>
+        <v>15.34758500991934</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09481515907856262</v>
+        <v>0.0945175761641677</v>
       </c>
       <c r="C52">
-        <v>1045.697142273267</v>
+        <v>1045.779808489127</v>
       </c>
       <c r="D52">
-        <v>1390.997142273267</v>
+        <v>1399.493808489127</v>
       </c>
       <c r="E52">
-        <v>-348.3</v>
+        <v>-339.886</v>
       </c>
       <c r="F52">
-        <v>420.7</v>
+        <v>429.114</v>
       </c>
       <c r="G52">
         <v>75.40000000000001</v>
@@ -5551,28 +5551,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M52">
-        <v>21.16121</v>
+        <v>21.5844342</v>
       </c>
       <c r="N52">
-        <v>303.6122593877552</v>
+        <v>303.1890351877552</v>
       </c>
       <c r="O52">
-        <v>91.08367781632654</v>
+        <v>90.95671055632654</v>
       </c>
       <c r="P52">
-        <v>212.5285815714286</v>
+        <v>212.2323246314286</v>
       </c>
       <c r="Q52">
-        <v>336.4285815714286</v>
+        <v>336.1323246314286</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1544203181571253</v>
+        <v>0.1562458697227912</v>
       </c>
       <c r="T52">
-        <v>0.7573489286396663</v>
+        <v>0.7700774820621817</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>15.34758500991934</v>
+        <v>15.04665197050916</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0945175761641677</v>
+        <v>0.09421999324977276</v>
       </c>
       <c r="C53">
-        <v>1045.779808489127</v>
+        <v>1045.966913492582</v>
       </c>
       <c r="D53">
-        <v>1399.493808489127</v>
+        <v>1408.094913492582</v>
       </c>
       <c r="E53">
-        <v>-339.886</v>
+        <v>-331.472</v>
       </c>
       <c r="F53">
-        <v>429.114</v>
+        <v>437.528</v>
       </c>
       <c r="G53">
         <v>75.40000000000001</v>
@@ -5633,28 +5633,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M53">
-        <v>21.5844342</v>
+        <v>22.0076584</v>
       </c>
       <c r="N53">
-        <v>303.1890351877552</v>
+        <v>302.7658109877551</v>
       </c>
       <c r="O53">
-        <v>90.95671055632654</v>
+        <v>90.82974329632653</v>
       </c>
       <c r="P53">
-        <v>212.2323246314286</v>
+        <v>211.9360676914286</v>
       </c>
       <c r="Q53">
-        <v>336.1323246314286</v>
+        <v>335.8360676914286</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1562458697227912</v>
+        <v>0.1581474859370266</v>
       </c>
       <c r="T53">
-        <v>0.7700774820621817</v>
+        <v>0.7833363918773019</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>15.04665197050916</v>
+        <v>14.75729327876859</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09421999324977276</v>
+        <v>0.09392241033537785</v>
       </c>
       <c r="C54">
-        <v>1045.966913492582</v>
+        <v>1046.260394792489</v>
       </c>
       <c r="D54">
-        <v>1408.094913492582</v>
+        <v>1416.802394792489</v>
       </c>
       <c r="E54">
-        <v>-331.472</v>
+        <v>-323.058</v>
       </c>
       <c r="F54">
-        <v>437.528</v>
+        <v>445.942</v>
       </c>
       <c r="G54">
         <v>75.40000000000001</v>
@@ -5715,28 +5715,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M54">
-        <v>22.0076584</v>
+        <v>22.4308826</v>
       </c>
       <c r="N54">
-        <v>302.7658109877551</v>
+        <v>302.3425867877551</v>
       </c>
       <c r="O54">
-        <v>90.82974329632653</v>
+        <v>90.70277603632654</v>
       </c>
       <c r="P54">
-        <v>211.9360676914286</v>
+        <v>211.6398107514286</v>
       </c>
       <c r="Q54">
-        <v>335.8360676914286</v>
+        <v>335.5398107514285</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1581474859370266</v>
+        <v>0.1601300219901656</v>
       </c>
       <c r="T54">
-        <v>0.7833363918773019</v>
+        <v>0.7971595106207251</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>14.75729327876859</v>
+        <v>14.47885378294277</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09392241033537785</v>
+        <v>0.09362482742098291</v>
       </c>
       <c r="C55">
-        <v>1046.260394792489</v>
+        <v>1046.66223812116</v>
       </c>
       <c r="D55">
-        <v>1416.802394792489</v>
+        <v>1425.618238121159</v>
       </c>
       <c r="E55">
-        <v>-323.058</v>
+        <v>-314.644</v>
       </c>
       <c r="F55">
-        <v>445.942</v>
+        <v>454.356</v>
       </c>
       <c r="G55">
         <v>75.40000000000001</v>
@@ -5797,28 +5797,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M55">
-        <v>22.4308826</v>
+        <v>22.8541068</v>
       </c>
       <c r="N55">
-        <v>302.3425867877551</v>
+        <v>301.9193625877551</v>
       </c>
       <c r="O55">
-        <v>90.70277603632654</v>
+        <v>90.57580877632654</v>
       </c>
       <c r="P55">
-        <v>211.6398107514286</v>
+        <v>211.3435538114286</v>
       </c>
       <c r="Q55">
-        <v>335.5398107514285</v>
+        <v>335.2435538114286</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1601300219901656</v>
+        <v>0.1621987552630063</v>
       </c>
       <c r="T55">
-        <v>0.7971595106207251</v>
+        <v>0.8115836345269059</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>14.47885378294277</v>
+        <v>14.21072686103642</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09362482742098291</v>
+        <v>0.09332724450658797</v>
       </c>
       <c r="C56">
-        <v>1046.66223812116</v>
+        <v>1047.17447894406</v>
       </c>
       <c r="D56">
-        <v>1425.618238121159</v>
+        <v>1434.54447894406</v>
       </c>
       <c r="E56">
-        <v>-314.644</v>
+        <v>-306.23</v>
       </c>
       <c r="F56">
-        <v>454.356</v>
+        <v>462.77</v>
       </c>
       <c r="G56">
         <v>75.40000000000001</v>
@@ -5879,28 +5879,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M56">
-        <v>22.8541068</v>
+        <v>23.277331</v>
       </c>
       <c r="N56">
-        <v>301.9193625877551</v>
+        <v>301.4961383877551</v>
       </c>
       <c r="O56">
-        <v>90.57580877632654</v>
+        <v>90.44884151632654</v>
       </c>
       <c r="P56">
-        <v>211.3435538114286</v>
+        <v>211.0472968714286</v>
       </c>
       <c r="Q56">
-        <v>335.2435538114286</v>
+        <v>334.9472968714286</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1621987552630063</v>
+        <v>0.1643594322368622</v>
       </c>
       <c r="T56">
-        <v>0.8115836345269059</v>
+        <v>0.8266488306066946</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>14.21072686103642</v>
+        <v>13.95235000901758</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09332724450658797</v>
+        <v>0.09302966159219306</v>
       </c>
       <c r="C57">
-        <v>1047.17447894406</v>
+        <v>1047.799204026602</v>
       </c>
       <c r="D57">
-        <v>1434.54447894406</v>
+        <v>1443.583204026601</v>
       </c>
       <c r="E57">
-        <v>-306.23</v>
+        <v>-297.816</v>
       </c>
       <c r="F57">
-        <v>462.77</v>
+        <v>471.184</v>
       </c>
       <c r="G57">
         <v>75.40000000000001</v>
@@ -5961,28 +5961,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M57">
-        <v>23.277331</v>
+        <v>23.7005552</v>
       </c>
       <c r="N57">
-        <v>301.4961383877551</v>
+        <v>301.0729141877551</v>
       </c>
       <c r="O57">
-        <v>90.44884151632654</v>
+        <v>90.32187425632654</v>
       </c>
       <c r="P57">
-        <v>211.0472968714286</v>
+        <v>210.7510399314286</v>
       </c>
       <c r="Q57">
-        <v>334.9472968714286</v>
+        <v>334.6510399314286</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1643594322368622</v>
+        <v>0.1666183218004388</v>
       </c>
       <c r="T57">
-        <v>0.8266488306066946</v>
+        <v>0.8423988083264738</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>13.95235000901758</v>
+        <v>13.70320090171369</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09302966159219306</v>
+        <v>0.09273207867779812</v>
       </c>
       <c r="C58">
-        <v>1047.799204026602</v>
+        <v>1048.538553060533</v>
       </c>
       <c r="D58">
-        <v>1443.583204026601</v>
+        <v>1452.736553060533</v>
       </c>
       <c r="E58">
-        <v>-297.816</v>
+        <v>-289.402</v>
       </c>
       <c r="F58">
-        <v>471.184</v>
+        <v>479.598</v>
       </c>
       <c r="G58">
         <v>75.40000000000001</v>
@@ -6043,28 +6043,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M58">
-        <v>23.7005552</v>
+        <v>24.1237794</v>
       </c>
       <c r="N58">
-        <v>301.0729141877551</v>
+        <v>300.6496899877552</v>
       </c>
       <c r="O58">
-        <v>90.32187425632654</v>
+        <v>90.19490699632654</v>
       </c>
       <c r="P58">
-        <v>210.7510399314286</v>
+        <v>210.4547829914286</v>
       </c>
       <c r="Q58">
-        <v>334.6510399314286</v>
+        <v>334.3547829914286</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1666183218004388</v>
+        <v>0.1689822759948794</v>
       </c>
       <c r="T58">
-        <v>0.8423988083264738</v>
+        <v>0.8588813431494985</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>13.70320090171369</v>
+        <v>13.46279386835029</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09273207867779812</v>
+        <v>0.09243449576340319</v>
       </c>
       <c r="C59">
-        <v>1048.538553060533</v>
+        <v>1049.394720352597</v>
       </c>
       <c r="D59">
-        <v>1452.736553060533</v>
+        <v>1462.006720352597</v>
       </c>
       <c r="E59">
-        <v>-289.402</v>
+        <v>-280.9879999999999</v>
       </c>
       <c r="F59">
-        <v>479.598</v>
+        <v>488.0120000000001</v>
       </c>
       <c r="G59">
         <v>75.40000000000001</v>
@@ -6125,28 +6125,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M59">
-        <v>24.1237794</v>
+        <v>24.5470036</v>
       </c>
       <c r="N59">
-        <v>300.6496899877552</v>
+        <v>300.2264657877552</v>
       </c>
       <c r="O59">
-        <v>90.19490699632654</v>
+        <v>90.06793973632655</v>
       </c>
       <c r="P59">
-        <v>210.4547829914286</v>
+        <v>210.1585260514286</v>
       </c>
       <c r="Q59">
-        <v>334.3547829914286</v>
+        <v>334.0585260514286</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1689822759948794</v>
+        <v>0.1714587994366743</v>
       </c>
       <c r="T59">
-        <v>0.8588813431494985</v>
+        <v>0.8761487605831434</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>13.46279386835029</v>
+        <v>13.23067673268908</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09243449576340321</v>
+        <v>0.09213691284900827</v>
       </c>
       <c r="C60">
-        <v>1049.394720352597</v>
+        <v>1050.369956578264</v>
       </c>
       <c r="D60">
-        <v>1462.006720352596</v>
+        <v>1471.395956578264</v>
       </c>
       <c r="E60">
-        <v>-280.9880000000001</v>
+        <v>-272.574</v>
       </c>
       <c r="F60">
-        <v>488.0119999999999</v>
+        <v>496.426</v>
       </c>
       <c r="G60">
         <v>75.40000000000001</v>
@@ -6207,28 +6207,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M60">
-        <v>24.5470036</v>
+        <v>24.9702278</v>
       </c>
       <c r="N60">
-        <v>300.2264657877552</v>
+        <v>299.8032415877552</v>
       </c>
       <c r="O60">
-        <v>90.06793973632655</v>
+        <v>89.94097247632655</v>
       </c>
       <c r="P60">
-        <v>210.1585260514286</v>
+        <v>209.8622691114286</v>
       </c>
       <c r="Q60">
-        <v>334.0585260514286</v>
+        <v>333.7622691114286</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1714587994366743</v>
+        <v>0.1740561289000202</v>
       </c>
       <c r="T60">
-        <v>0.8761487605831432</v>
+        <v>0.8942584910623318</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>13.23067673268909</v>
+        <v>13.00642797450791</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09213691284900827</v>
+        <v>0.09246932993461336</v>
       </c>
       <c r="C61">
-        <v>1050.369956578264</v>
+        <v>1031.475472792829</v>
       </c>
       <c r="D61">
-        <v>1471.395956578264</v>
+        <v>1460.915472792828</v>
       </c>
       <c r="E61">
-        <v>-272.574</v>
+        <v>-264.16</v>
       </c>
       <c r="F61">
-        <v>496.426</v>
+        <v>504.84</v>
       </c>
       <c r="G61">
         <v>75.40000000000001</v>
@@ -6289,45 +6289,45 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M61">
-        <v>24.9702278</v>
+        <v>26.150712</v>
       </c>
       <c r="N61">
-        <v>299.8032415877552</v>
+        <v>298.6227573877551</v>
       </c>
       <c r="O61">
-        <v>89.94097247632655</v>
+        <v>89.58682721632654</v>
       </c>
       <c r="P61">
-        <v>209.8622691114286</v>
+        <v>209.0359301714286</v>
       </c>
       <c r="Q61">
-        <v>333.7622691114286</v>
+        <v>332.9359301714286</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1740561289000202</v>
+        <v>0.1767833248365334</v>
       </c>
       <c r="T61">
-        <v>0.8942584910623318</v>
+        <v>0.9132737080654799</v>
       </c>
       <c r="U61">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y61">
-        <v>13.00642797450791</v>
+        <v>12.41929739380538</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09246932993461336</v>
+        <v>0.09218224702021843</v>
       </c>
       <c r="C62">
-        <v>1031.475472792829</v>
+        <v>1032.103809000283</v>
       </c>
       <c r="D62">
-        <v>1460.915472792828</v>
+        <v>1469.957809000283</v>
       </c>
       <c r="E62">
-        <v>-264.16</v>
+        <v>-255.746</v>
       </c>
       <c r="F62">
-        <v>504.84</v>
+        <v>513.254</v>
       </c>
       <c r="G62">
         <v>75.40000000000001</v>
@@ -6371,28 +6371,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M62">
-        <v>26.150712</v>
+        <v>26.5865572</v>
       </c>
       <c r="N62">
-        <v>298.6227573877551</v>
+        <v>298.1869121877551</v>
       </c>
       <c r="O62">
-        <v>89.58682721632654</v>
+        <v>89.45607365632654</v>
       </c>
       <c r="P62">
-        <v>209.0359301714286</v>
+        <v>208.7308385314286</v>
       </c>
       <c r="Q62">
-        <v>332.9359301714286</v>
+        <v>332.6308385314286</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1767833248365334</v>
+        <v>0.179650376974919</v>
       </c>
       <c r="T62">
-        <v>0.9132737080654799</v>
+        <v>0.9332640644021226</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>12.41929739380538</v>
+        <v>12.21570235456267</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09218224702021843</v>
+        <v>0.09189516410582349</v>
       </c>
       <c r="C63">
-        <v>1032.103809000283</v>
+        <v>1032.84477742336</v>
       </c>
       <c r="D63">
-        <v>1469.957809000283</v>
+        <v>1479.112777423361</v>
       </c>
       <c r="E63">
-        <v>-255.746</v>
+        <v>-247.332</v>
       </c>
       <c r="F63">
-        <v>513.254</v>
+        <v>521.668</v>
       </c>
       <c r="G63">
         <v>75.40000000000001</v>
@@ -6453,28 +6453,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M63">
-        <v>26.5865572</v>
+        <v>27.0224024</v>
       </c>
       <c r="N63">
-        <v>298.1869121877551</v>
+        <v>297.7510669877552</v>
       </c>
       <c r="O63">
-        <v>89.45607365632654</v>
+        <v>89.32532009632655</v>
       </c>
       <c r="P63">
-        <v>208.7308385314286</v>
+        <v>208.4257468914286</v>
       </c>
       <c r="Q63">
-        <v>332.6308385314286</v>
+        <v>332.3257468914286</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.179650376974919</v>
+        <v>0.1826683265942724</v>
       </c>
       <c r="T63">
-        <v>0.9332640644021226</v>
+        <v>0.9543065447564835</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>12.21570235456267</v>
+        <v>12.01867489723102</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09189516410582349</v>
+        <v>0.09160808119142858</v>
       </c>
       <c r="C64">
-        <v>1032.84477742336</v>
+        <v>1033.700495687415</v>
       </c>
       <c r="D64">
-        <v>1479.112777423361</v>
+        <v>1488.382495687415</v>
       </c>
       <c r="E64">
-        <v>-247.332</v>
+        <v>-238.918</v>
       </c>
       <c r="F64">
-        <v>521.668</v>
+        <v>530.082</v>
       </c>
       <c r="G64">
         <v>75.40000000000001</v>
@@ -6535,28 +6535,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M64">
-        <v>27.0224024</v>
+        <v>27.4582476</v>
       </c>
       <c r="N64">
-        <v>297.7510669877552</v>
+        <v>297.3152217877551</v>
       </c>
       <c r="O64">
-        <v>89.32532009632655</v>
+        <v>89.19456653632655</v>
       </c>
       <c r="P64">
-        <v>208.4257468914286</v>
+        <v>208.1206552514286</v>
       </c>
       <c r="Q64">
-        <v>332.3257468914286</v>
+        <v>332.0206552514286</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1826683265942724</v>
+        <v>0.1858494086254826</v>
       </c>
       <c r="T64">
-        <v>0.9543065447564835</v>
+        <v>0.9764864564813504</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>12.01867489723102</v>
+        <v>11.82790227981465</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09160808119142858</v>
+        <v>0.09132099827703363</v>
       </c>
       <c r="C65">
-        <v>1033.700495687415</v>
+        <v>1034.673134837899</v>
       </c>
       <c r="D65">
-        <v>1488.382495687415</v>
+        <v>1497.769134837899</v>
       </c>
       <c r="E65">
-        <v>-238.918</v>
+        <v>-230.504</v>
       </c>
       <c r="F65">
-        <v>530.082</v>
+        <v>538.496</v>
       </c>
       <c r="G65">
         <v>75.40000000000001</v>
@@ -6617,28 +6617,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M65">
-        <v>27.4582476</v>
+        <v>27.8940928</v>
       </c>
       <c r="N65">
-        <v>297.3152217877551</v>
+        <v>296.8793765877551</v>
       </c>
       <c r="O65">
-        <v>89.19456653632655</v>
+        <v>89.06381297632653</v>
       </c>
       <c r="P65">
-        <v>208.1206552514286</v>
+        <v>207.8155636114286</v>
       </c>
       <c r="Q65">
-        <v>332.0206552514286</v>
+        <v>331.7155636114286</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1858494086254826</v>
+        <v>0.1892072174362046</v>
       </c>
       <c r="T65">
-        <v>0.9764864564813504</v>
+        <v>0.9998985855242654</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>11.82790227981465</v>
+        <v>11.64309130669255</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09132099827703363</v>
+        <v>0.0910339153626387</v>
       </c>
       <c r="C66">
-        <v>1034.673134837899</v>
+        <v>1035.764921035554</v>
       </c>
       <c r="D66">
-        <v>1497.769134837899</v>
+        <v>1507.274921035554</v>
       </c>
       <c r="E66">
-        <v>-230.504</v>
+        <v>-222.09</v>
       </c>
       <c r="F66">
-        <v>538.496</v>
+        <v>546.91</v>
       </c>
       <c r="G66">
         <v>75.40000000000001</v>
@@ -6699,28 +6699,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M66">
-        <v>27.8940928</v>
+        <v>28.329938</v>
       </c>
       <c r="N66">
-        <v>296.8793765877551</v>
+        <v>296.4435313877551</v>
       </c>
       <c r="O66">
-        <v>89.06381297632653</v>
+        <v>88.93305941632653</v>
       </c>
       <c r="P66">
-        <v>207.8155636114286</v>
+        <v>207.5104719714286</v>
       </c>
       <c r="Q66">
-        <v>331.7155636114286</v>
+        <v>331.4104719714286</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1892072174362046</v>
+        <v>0.1927569010361106</v>
       </c>
       <c r="T66">
-        <v>0.9998985855242654</v>
+        <v>1.02464855051249</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>11.64309130669255</v>
+        <v>11.46396682505112</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0910339153626387</v>
+        <v>0.09074683244824379</v>
       </c>
       <c r="C67">
-        <v>1035.764921035554</v>
+        <v>1036.978137316557</v>
       </c>
       <c r="D67">
-        <v>1507.274921035554</v>
+        <v>1516.902137316557</v>
       </c>
       <c r="E67">
-        <v>-222.09</v>
+        <v>-213.676</v>
       </c>
       <c r="F67">
-        <v>546.91</v>
+        <v>555.324</v>
       </c>
       <c r="G67">
         <v>75.40000000000001</v>
@@ -6781,28 +6781,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M67">
-        <v>28.329938</v>
+        <v>28.7657832</v>
       </c>
       <c r="N67">
-        <v>296.4435313877551</v>
+        <v>296.0076861877552</v>
       </c>
       <c r="O67">
-        <v>88.93305941632653</v>
+        <v>88.80230585632654</v>
       </c>
       <c r="P67">
-        <v>207.5104719714286</v>
+        <v>207.2053803314286</v>
       </c>
       <c r="Q67">
-        <v>331.4104719714286</v>
+        <v>331.1053803314286</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1927569010361106</v>
+        <v>0.1965153895536582</v>
       </c>
       <c r="T67">
-        <v>1.02464855051249</v>
+        <v>1.050854395794139</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>11.46396682505112</v>
+        <v>11.29027035800489</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09074683244824379</v>
+        <v>0.09045974953384887</v>
       </c>
       <c r="C68">
-        <v>1036.978137316557</v>
+        <v>1038.315125420569</v>
       </c>
       <c r="D68">
-        <v>1516.902137316557</v>
+        <v>1526.653125420569</v>
       </c>
       <c r="E68">
-        <v>-213.676</v>
+        <v>-205.2619999999999</v>
       </c>
       <c r="F68">
-        <v>555.324</v>
+        <v>563.7380000000001</v>
       </c>
       <c r="G68">
         <v>75.40000000000001</v>
@@ -6863,28 +6863,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M68">
-        <v>28.7657832</v>
+        <v>29.2016284</v>
       </c>
       <c r="N68">
-        <v>296.0076861877552</v>
+        <v>295.5718409877551</v>
       </c>
       <c r="O68">
-        <v>88.80230585632654</v>
+        <v>88.67155229632654</v>
       </c>
       <c r="P68">
-        <v>207.2053803314286</v>
+        <v>206.9002886914286</v>
       </c>
       <c r="Q68">
-        <v>331.1053803314286</v>
+        <v>330.8002886914286</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1965153895536582</v>
+        <v>0.2005016652540875</v>
       </c>
       <c r="T68">
-        <v>1.050854395794139</v>
+        <v>1.078648474123161</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>11.29027035800489</v>
+        <v>11.12175886012422</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09045974953384887</v>
+        <v>0.09017266661945393</v>
       </c>
       <c r="C69">
-        <v>1038.315125420569</v>
+        <v>1039.778287689733</v>
       </c>
       <c r="D69">
-        <v>1526.653125420569</v>
+        <v>1536.530287689733</v>
       </c>
       <c r="E69">
-        <v>-205.2619999999999</v>
+        <v>-196.848</v>
       </c>
       <c r="F69">
-        <v>563.7380000000001</v>
+        <v>572.152</v>
       </c>
       <c r="G69">
         <v>75.40000000000001</v>
@@ -6945,28 +6945,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M69">
-        <v>29.2016284</v>
+        <v>29.6374736</v>
       </c>
       <c r="N69">
-        <v>295.5718409877551</v>
+        <v>295.1359957877551</v>
       </c>
       <c r="O69">
-        <v>88.67155229632654</v>
+        <v>88.54079873632654</v>
       </c>
       <c r="P69">
-        <v>206.9002886914286</v>
+        <v>206.5951970514286</v>
       </c>
       <c r="Q69">
-        <v>330.8002886914286</v>
+        <v>330.4951970514286</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2005016652540875</v>
+        <v>0.2047370831857936</v>
       </c>
       <c r="T69">
-        <v>1.078648474123161</v>
+        <v>1.108179682347747</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>11.12175886012422</v>
+        <v>10.95820358276946</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09017266661945393</v>
+        <v>0.089885583705059</v>
       </c>
       <c r="C70">
-        <v>1039.778287689733</v>
+        <v>1041.370089041875</v>
       </c>
       <c r="D70">
-        <v>1536.530287689733</v>
+        <v>1546.536089041875</v>
       </c>
       <c r="E70">
-        <v>-196.848</v>
+        <v>-188.434</v>
       </c>
       <c r="F70">
-        <v>572.152</v>
+        <v>580.566</v>
       </c>
       <c r="G70">
         <v>75.40000000000001</v>
@@ -7027,28 +7027,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M70">
-        <v>29.6374736</v>
+        <v>30.0733188</v>
       </c>
       <c r="N70">
-        <v>295.1359957877551</v>
+        <v>294.7001505877552</v>
       </c>
       <c r="O70">
-        <v>88.54079873632654</v>
+        <v>88.41004517632655</v>
       </c>
       <c r="P70">
-        <v>206.5951970514286</v>
+        <v>206.2901054114286</v>
       </c>
       <c r="Q70">
-        <v>330.4951970514286</v>
+        <v>330.1901054114286</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2047370831857936</v>
+        <v>0.2092457538872872</v>
       </c>
       <c r="T70">
-        <v>1.108179682347747</v>
+        <v>1.139616129812629</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>10.95820358276946</v>
+        <v>10.79938903809164</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.089885583705059</v>
+        <v>0.08959850079066407</v>
       </c>
       <c r="C71">
-        <v>1041.370089041875</v>
+        <v>1043.093059021307</v>
       </c>
       <c r="D71">
-        <v>1546.536089041875</v>
+        <v>1556.673059021307</v>
       </c>
       <c r="E71">
-        <v>-188.434</v>
+        <v>-180.02</v>
       </c>
       <c r="F71">
-        <v>580.566</v>
+        <v>588.98</v>
       </c>
       <c r="G71">
         <v>75.40000000000001</v>
@@ -7109,28 +7109,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M71">
-        <v>30.0733188</v>
+        <v>30.509164</v>
       </c>
       <c r="N71">
-        <v>294.7001505877552</v>
+        <v>294.2643053877551</v>
       </c>
       <c r="O71">
-        <v>88.41004517632655</v>
+        <v>88.27929161632655</v>
       </c>
       <c r="P71">
-        <v>206.2901054114286</v>
+        <v>205.9850137714286</v>
       </c>
       <c r="Q71">
-        <v>330.1901054114286</v>
+        <v>329.8850137714286</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2092457538872872</v>
+        <v>0.214055002635547</v>
       </c>
       <c r="T71">
-        <v>1.139616129812629</v>
+        <v>1.173148340441836</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>10.79938903809164</v>
+        <v>10.64511205183318</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08959850079066407</v>
+        <v>0.08931141787626914</v>
       </c>
       <c r="C72">
-        <v>1043.093059021307</v>
+        <v>1044.949793930813</v>
       </c>
       <c r="D72">
-        <v>1556.673059021307</v>
+        <v>1566.943793930813</v>
       </c>
       <c r="E72">
-        <v>-180.02</v>
+        <v>-171.606</v>
       </c>
       <c r="F72">
-        <v>588.98</v>
+        <v>597.394</v>
       </c>
       <c r="G72">
         <v>75.40000000000001</v>
@@ -7191,28 +7191,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M72">
-        <v>30.509164</v>
+        <v>30.9450092</v>
       </c>
       <c r="N72">
-        <v>294.2643053877551</v>
+        <v>293.8284601877551</v>
       </c>
       <c r="O72">
-        <v>88.27929161632655</v>
+        <v>88.14853805632653</v>
       </c>
       <c r="P72">
-        <v>205.9850137714286</v>
+        <v>205.6799221314286</v>
       </c>
       <c r="Q72">
-        <v>329.8850137714286</v>
+        <v>329.5799221314286</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.214055002635547</v>
+        <v>0.219195923711273</v>
       </c>
       <c r="T72">
-        <v>1.173148340441836</v>
+        <v>1.208993117321334</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>10.64511205183318</v>
+        <v>10.49518089617356</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08931141787626916</v>
+        <v>0.08902433496187423</v>
       </c>
       <c r="C73">
-        <v>1044.949793930813</v>
+        <v>1046.942959048599</v>
       </c>
       <c r="D73">
-        <v>1566.943793930813</v>
+        <v>1577.350959048598</v>
       </c>
       <c r="E73">
-        <v>-171.606</v>
+        <v>-163.192</v>
       </c>
       <c r="F73">
-        <v>597.394</v>
+        <v>605.808</v>
       </c>
       <c r="G73">
         <v>75.40000000000001</v>
@@ -7273,28 +7273,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M73">
-        <v>30.9450092</v>
+        <v>31.3808544</v>
       </c>
       <c r="N73">
-        <v>293.8284601877551</v>
+        <v>293.3926149877552</v>
       </c>
       <c r="O73">
-        <v>88.14853805632653</v>
+        <v>88.01778449632654</v>
       </c>
       <c r="P73">
-        <v>205.6799221314286</v>
+        <v>205.3748304914286</v>
       </c>
       <c r="Q73">
-        <v>329.5799221314286</v>
+        <v>329.2748304914286</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2191959237112729</v>
+        <v>0.2247040534352651</v>
       </c>
       <c r="T73">
-        <v>1.208993117321333</v>
+        <v>1.247398235406509</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>10.49518089617356</v>
+        <v>10.34941449483782</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08902433496187423</v>
+        <v>0.0887372520474793</v>
       </c>
       <c r="C74">
-        <v>1046.942959048599</v>
+        <v>1049.075290934173</v>
       </c>
       <c r="D74">
-        <v>1577.350959048598</v>
+        <v>1587.897290934173</v>
       </c>
       <c r="E74">
-        <v>-163.192</v>
+        <v>-154.778</v>
       </c>
       <c r="F74">
-        <v>605.808</v>
+        <v>614.222</v>
       </c>
       <c r="G74">
         <v>75.40000000000001</v>
@@ -7355,28 +7355,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M74">
-        <v>31.3808544</v>
+        <v>31.8166996</v>
       </c>
       <c r="N74">
-        <v>293.3926149877552</v>
+        <v>292.9567697877551</v>
       </c>
       <c r="O74">
-        <v>88.01778449632654</v>
+        <v>87.88703093632654</v>
       </c>
       <c r="P74">
-        <v>205.3748304914286</v>
+        <v>205.0697388514286</v>
       </c>
       <c r="Q74">
-        <v>329.2748304914286</v>
+        <v>328.9697388514286</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2247040534352651</v>
+        <v>0.2306201927684419</v>
       </c>
       <c r="T74">
-        <v>1.247398235406509</v>
+        <v>1.28864817705355</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>10.34941449483782</v>
+        <v>10.20764169353867</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0887372520474793</v>
+        <v>0.08845016913308437</v>
       </c>
       <c r="C75">
-        <v>1049.075290934173</v>
+        <v>1051.349599827364</v>
       </c>
       <c r="D75">
-        <v>1587.897290934173</v>
+        <v>1598.585599827363</v>
       </c>
       <c r="E75">
-        <v>-154.778</v>
+        <v>-146.364</v>
       </c>
       <c r="F75">
-        <v>614.222</v>
+        <v>622.636</v>
       </c>
       <c r="G75">
         <v>75.40000000000001</v>
@@ -7437,28 +7437,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M75">
-        <v>31.8166996</v>
+        <v>32.2525448</v>
       </c>
       <c r="N75">
-        <v>292.9567697877551</v>
+        <v>292.5209245877551</v>
       </c>
       <c r="O75">
-        <v>87.88703093632654</v>
+        <v>87.75627737632654</v>
       </c>
       <c r="P75">
-        <v>205.0697388514286</v>
+        <v>204.7646472114286</v>
       </c>
       <c r="Q75">
-        <v>328.9697388514286</v>
+        <v>328.6646472114286</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2306201927684419</v>
+        <v>0.2369914197426322</v>
       </c>
       <c r="T75">
-        <v>1.28864817705355</v>
+        <v>1.333071191134978</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>10.20764169353867</v>
+        <v>10.06970058957193</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08845016913308437</v>
+        <v>0.08816308621868944</v>
       </c>
       <c r="C76">
-        <v>1051.349599827364</v>
+        <v>1053.768772144864</v>
       </c>
       <c r="D76">
-        <v>1598.585599827363</v>
+        <v>1609.418772144864</v>
       </c>
       <c r="E76">
-        <v>-146.364</v>
+        <v>-137.95</v>
       </c>
       <c r="F76">
-        <v>622.636</v>
+        <v>631.05</v>
       </c>
       <c r="G76">
         <v>75.40000000000001</v>
@@ -7519,28 +7519,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M76">
-        <v>32.2525448</v>
+        <v>32.68839</v>
       </c>
       <c r="N76">
-        <v>292.5209245877551</v>
+        <v>292.0850793877552</v>
       </c>
       <c r="O76">
-        <v>87.75627737632654</v>
+        <v>87.62552381632655</v>
       </c>
       <c r="P76">
-        <v>204.7646472114286</v>
+        <v>204.4595555714286</v>
       </c>
       <c r="Q76">
-        <v>328.6646472114286</v>
+        <v>328.3595555714286</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2369914197426322</v>
+        <v>0.2438723448747578</v>
       </c>
       <c r="T76">
-        <v>1.333071191134978</v>
+        <v>1.381048046342921</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>10.06970058957193</v>
+        <v>9.935437915044307</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08816308621868944</v>
+        <v>0.08878040330429453</v>
       </c>
       <c r="C77">
-        <v>1053.768772144864</v>
+        <v>1022.239081514774</v>
       </c>
       <c r="D77">
-        <v>1609.418772144864</v>
+        <v>1586.303081514774</v>
       </c>
       <c r="E77">
-        <v>-137.95</v>
+        <v>-129.5360000000001</v>
       </c>
       <c r="F77">
-        <v>631.05</v>
+        <v>639.4639999999999</v>
       </c>
       <c r="G77">
         <v>75.40000000000001</v>
@@ -7601,45 +7601,45 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M77">
-        <v>32.68839</v>
+        <v>34.211324</v>
       </c>
       <c r="N77">
-        <v>292.0850793877552</v>
+        <v>290.5621453877552</v>
       </c>
       <c r="O77">
-        <v>87.62552381632655</v>
+        <v>87.16864361632655</v>
       </c>
       <c r="P77">
-        <v>204.4595555714286</v>
+        <v>203.3935017714286</v>
       </c>
       <c r="Q77">
-        <v>328.3595555714286</v>
+        <v>327.2935017714286</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2438723448747578</v>
+        <v>0.2513266804345605</v>
       </c>
       <c r="T77">
-        <v>1.381048046342921</v>
+        <v>1.433022972818192</v>
       </c>
       <c r="U77">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V77">
         <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>9.935437915044307</v>
+        <v>9.493156984738595</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08878040330429453</v>
+        <v>0.08850522038989959</v>
       </c>
       <c r="C78">
-        <v>1022.239081514774</v>
+        <v>1024.046864732363</v>
       </c>
       <c r="D78">
-        <v>1586.303081514774</v>
+        <v>1596.524864732363</v>
       </c>
       <c r="E78">
-        <v>-129.5360000000001</v>
+        <v>-121.122</v>
       </c>
       <c r="F78">
-        <v>639.4639999999999</v>
+        <v>647.878</v>
       </c>
       <c r="G78">
         <v>75.40000000000001</v>
@@ -7683,28 +7683,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M78">
-        <v>34.211324</v>
+        <v>34.661473</v>
       </c>
       <c r="N78">
-        <v>290.5621453877552</v>
+        <v>290.1119963877551</v>
       </c>
       <c r="O78">
-        <v>87.16864361632655</v>
+        <v>87.03359891632654</v>
       </c>
       <c r="P78">
-        <v>203.3935017714286</v>
+        <v>203.0783974714286</v>
       </c>
       <c r="Q78">
-        <v>327.2935017714286</v>
+        <v>326.9783974714286</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2513266804345605</v>
+        <v>0.25942921908652</v>
       </c>
       <c r="T78">
-        <v>1.433022972818192</v>
+        <v>1.4895174581174</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>9.493156984738595</v>
+        <v>9.369869231690043</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08850522038989959</v>
+        <v>0.08823003747550466</v>
       </c>
       <c r="C79">
-        <v>1024.046864732363</v>
+        <v>1025.987236100398</v>
       </c>
       <c r="D79">
-        <v>1596.524864732363</v>
+        <v>1606.879236100398</v>
       </c>
       <c r="E79">
-        <v>-121.122</v>
+        <v>-112.708</v>
       </c>
       <c r="F79">
-        <v>647.878</v>
+        <v>656.292</v>
       </c>
       <c r="G79">
         <v>75.40000000000001</v>
@@ -7765,28 +7765,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M79">
-        <v>34.661473</v>
+        <v>35.111622</v>
       </c>
       <c r="N79">
-        <v>290.1119963877551</v>
+        <v>289.6618473877551</v>
       </c>
       <c r="O79">
-        <v>87.03359891632654</v>
+        <v>86.89855421632653</v>
       </c>
       <c r="P79">
-        <v>203.0783974714286</v>
+        <v>202.7632931714286</v>
       </c>
       <c r="Q79">
-        <v>326.9783974714286</v>
+        <v>326.6632931714286</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.25942921908652</v>
+        <v>0.2682683521613848</v>
       </c>
       <c r="T79">
-        <v>1.4895174581174</v>
+        <v>1.551147805716536</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>9.369869231690043</v>
+        <v>9.249742703078629</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08823003747550466</v>
+        <v>0.08795485456110974</v>
       </c>
       <c r="C80">
-        <v>1025.987236100398</v>
+        <v>1028.062792187699</v>
       </c>
       <c r="D80">
-        <v>1606.879236100398</v>
+        <v>1617.368792187699</v>
       </c>
       <c r="E80">
-        <v>-112.708</v>
+        <v>-104.294</v>
       </c>
       <c r="F80">
-        <v>656.292</v>
+        <v>664.706</v>
       </c>
       <c r="G80">
         <v>75.40000000000001</v>
@@ -7847,28 +7847,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M80">
-        <v>35.111622</v>
+        <v>35.561771</v>
       </c>
       <c r="N80">
-        <v>289.6618473877551</v>
+        <v>289.2116983877551</v>
       </c>
       <c r="O80">
-        <v>86.89855421632653</v>
+        <v>86.76350951632654</v>
       </c>
       <c r="P80">
-        <v>202.7632931714286</v>
+        <v>202.4481888714286</v>
       </c>
       <c r="Q80">
-        <v>326.6632931714286</v>
+        <v>326.3481888714285</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2682683521613848</v>
+        <v>0.2779493074338559</v>
       </c>
       <c r="T80">
-        <v>1.551147805716536</v>
+        <v>1.618647710229875</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>9.249742703078629</v>
+        <v>9.132657352406749</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08795485456110974</v>
+        <v>0.08767967164671481</v>
       </c>
       <c r="C81">
-        <v>1028.062792187699</v>
+        <v>1030.276197809217</v>
       </c>
       <c r="D81">
-        <v>1617.368792187699</v>
+        <v>1627.996197809217</v>
       </c>
       <c r="E81">
-        <v>-104.294</v>
+        <v>-95.88</v>
       </c>
       <c r="F81">
-        <v>664.706</v>
+        <v>673.12</v>
       </c>
       <c r="G81">
         <v>75.40000000000001</v>
@@ -7929,28 +7929,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M81">
-        <v>35.561771</v>
+        <v>36.01192</v>
       </c>
       <c r="N81">
-        <v>289.2116983877551</v>
+        <v>288.7615493877552</v>
       </c>
       <c r="O81">
-        <v>86.76350951632654</v>
+        <v>86.62846481632654</v>
       </c>
       <c r="P81">
-        <v>202.4481888714286</v>
+        <v>202.1330845714286</v>
       </c>
       <c r="Q81">
-        <v>326.3481888714285</v>
+        <v>326.0330845714286</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2779493074338559</v>
+        <v>0.2885983582335741</v>
       </c>
       <c r="T81">
-        <v>1.618647710229875</v>
+        <v>1.692897605194548</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>9.132657352406749</v>
+        <v>9.018499135501667</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08767967164671481</v>
+        <v>0.08740448873231987</v>
       </c>
       <c r="C82">
-        <v>1030.276197809217</v>
+        <v>1032.630188283019</v>
       </c>
       <c r="D82">
-        <v>1627.996197809217</v>
+        <v>1638.764188283019</v>
       </c>
       <c r="E82">
-        <v>-95.88</v>
+        <v>-87.46600000000001</v>
       </c>
       <c r="F82">
-        <v>673.12</v>
+        <v>681.534</v>
       </c>
       <c r="G82">
         <v>75.40000000000001</v>
@@ -8011,28 +8011,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M82">
-        <v>36.01192</v>
+        <v>36.462069</v>
       </c>
       <c r="N82">
-        <v>288.7615493877552</v>
+        <v>288.3114003877552</v>
       </c>
       <c r="O82">
-        <v>86.62846481632654</v>
+        <v>86.49342011632655</v>
       </c>
       <c r="P82">
-        <v>202.1330845714286</v>
+        <v>201.8179802714286</v>
       </c>
       <c r="Q82">
-        <v>326.0330845714286</v>
+        <v>325.7179802714286</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2885983582335741</v>
+        <v>0.3003683617490521</v>
       </c>
       <c r="T82">
-        <v>1.692897605194548</v>
+        <v>1.774963278576556</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>9.018499135501667</v>
+        <v>8.907159640001645</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08740448873231987</v>
+        <v>0.08712930581792497</v>
       </c>
       <c r="C83">
-        <v>1032.630188283019</v>
+        <v>1035.127571777443</v>
       </c>
       <c r="D83">
-        <v>1638.764188283019</v>
+        <v>1649.675571777443</v>
       </c>
       <c r="E83">
-        <v>-87.46600000000001</v>
+        <v>-79.05200000000002</v>
       </c>
       <c r="F83">
-        <v>681.534</v>
+        <v>689.948</v>
       </c>
       <c r="G83">
         <v>75.40000000000001</v>
@@ -8093,28 +8093,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M83">
-        <v>36.462069</v>
+        <v>36.912218</v>
       </c>
       <c r="N83">
-        <v>288.3114003877552</v>
+        <v>287.8612513877551</v>
       </c>
       <c r="O83">
-        <v>86.49342011632655</v>
+        <v>86.35837541632654</v>
       </c>
       <c r="P83">
-        <v>201.8179802714286</v>
+        <v>201.5028759714286</v>
       </c>
       <c r="Q83">
-        <v>325.7179802714286</v>
+        <v>325.4028759714286</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3003683617490521</v>
+        <v>0.3134461434329165</v>
       </c>
       <c r="T83">
-        <v>1.774963278576556</v>
+        <v>1.866147360112119</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>8.907159640001645</v>
+        <v>8.798535741952845</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08712930581792497</v>
+        <v>0.08685412290353003</v>
       </c>
       <c r="C84">
-        <v>1035.127571777443</v>
+        <v>1037.771231752656</v>
       </c>
       <c r="D84">
-        <v>1649.675571777443</v>
+        <v>1660.733231752656</v>
       </c>
       <c r="E84">
-        <v>-79.05200000000002</v>
+        <v>-70.63799999999992</v>
       </c>
       <c r="F84">
-        <v>689.948</v>
+        <v>698.3620000000001</v>
       </c>
       <c r="G84">
         <v>75.40000000000001</v>
@@ -8175,28 +8175,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M84">
-        <v>36.912218</v>
+        <v>37.36236700000001</v>
       </c>
       <c r="N84">
-        <v>287.8612513877551</v>
+        <v>287.4111023877551</v>
       </c>
       <c r="O84">
-        <v>86.35837541632654</v>
+        <v>86.22333071632654</v>
       </c>
       <c r="P84">
-        <v>201.5028759714286</v>
+        <v>201.1877716714286</v>
       </c>
       <c r="Q84">
-        <v>325.4028759714286</v>
+        <v>325.0877716714286</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3134461434329165</v>
+        <v>0.3280624876678238</v>
       </c>
       <c r="T84">
-        <v>1.866147360112119</v>
+        <v>1.968058980651867</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.798535741952845</v>
+        <v>8.692529287230521</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08685412290353003</v>
+        <v>0.0865789399891351</v>
       </c>
       <c r="C85">
-        <v>1037.771231752656</v>
+        <v>1040.564129501053</v>
       </c>
       <c r="D85">
-        <v>1660.733231752656</v>
+        <v>1671.940129501053</v>
       </c>
       <c r="E85">
-        <v>-70.63799999999992</v>
+        <v>-62.22399999999993</v>
       </c>
       <c r="F85">
-        <v>698.3620000000001</v>
+        <v>706.7760000000001</v>
       </c>
       <c r="G85">
         <v>75.40000000000001</v>
@@ -8257,28 +8257,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M85">
-        <v>37.36236700000001</v>
+        <v>37.812516</v>
       </c>
       <c r="N85">
-        <v>287.4111023877551</v>
+        <v>286.9609533877551</v>
       </c>
       <c r="O85">
-        <v>86.22333071632654</v>
+        <v>86.08828601632653</v>
       </c>
       <c r="P85">
-        <v>201.1877716714286</v>
+        <v>200.8726673714286</v>
       </c>
       <c r="Q85">
-        <v>325.0877716714286</v>
+        <v>324.7726673714286</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3280624876678238</v>
+        <v>0.3445058749320946</v>
       </c>
       <c r="T85">
-        <v>1.968058980651867</v>
+        <v>2.082709553759083</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>8.692529287230521</v>
+        <v>8.58904679571587</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08657893998913511</v>
+        <v>0.08630375707474018</v>
       </c>
       <c r="C86">
-        <v>1040.564129501052</v>
+        <v>1043.509306791222</v>
       </c>
       <c r="D86">
-        <v>1671.940129501052</v>
+        <v>1683.299306791221</v>
       </c>
       <c r="E86">
-        <v>-62.22400000000005</v>
+        <v>-53.81000000000006</v>
       </c>
       <c r="F86">
-        <v>706.776</v>
+        <v>715.1899999999999</v>
       </c>
       <c r="G86">
         <v>75.40000000000001</v>
@@ -8339,28 +8339,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M86">
-        <v>37.812516</v>
+        <v>38.262665</v>
       </c>
       <c r="N86">
-        <v>286.9609533877551</v>
+        <v>286.5108043877551</v>
       </c>
       <c r="O86">
-        <v>86.08828601632653</v>
+        <v>85.95324131632653</v>
       </c>
       <c r="P86">
-        <v>200.8726673714286</v>
+        <v>200.5575630714286</v>
       </c>
       <c r="Q86">
-        <v>324.7726673714286</v>
+        <v>324.4575630714286</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3445058749320944</v>
+        <v>0.3631417138316012</v>
       </c>
       <c r="T86">
-        <v>2.082709553759082</v>
+        <v>2.21264686994726</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>8.589046795715873</v>
+        <v>8.487999186354507</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08630375707474018</v>
+        <v>0.08602857416034526</v>
       </c>
       <c r="C87">
-        <v>1043.509306791222</v>
+        <v>1046.609888620432</v>
       </c>
       <c r="D87">
-        <v>1683.299306791221</v>
+        <v>1694.813888620432</v>
       </c>
       <c r="E87">
-        <v>-53.81000000000006</v>
+        <v>-45.39600000000007</v>
       </c>
       <c r="F87">
-        <v>715.1899999999999</v>
+        <v>723.6039999999999</v>
       </c>
       <c r="G87">
         <v>75.40000000000001</v>
@@ -8421,28 +8421,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M87">
-        <v>38.262665</v>
+        <v>38.71281399999999</v>
       </c>
       <c r="N87">
-        <v>286.5108043877551</v>
+        <v>286.0606553877552</v>
       </c>
       <c r="O87">
-        <v>85.95324131632653</v>
+        <v>85.81819661632655</v>
       </c>
       <c r="P87">
-        <v>200.5575630714286</v>
+        <v>200.2424587714286</v>
       </c>
       <c r="Q87">
-        <v>324.4575630714286</v>
+        <v>324.1424587714286</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3631417138316012</v>
+        <v>0.3844398154310375</v>
       </c>
       <c r="T87">
-        <v>2.21264686994726</v>
+        <v>2.361146659876606</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.487999186354507</v>
+        <v>8.389301521396899</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08602857416034526</v>
+        <v>0.08575339124595033</v>
       </c>
       <c r="C88">
-        <v>1046.609888620432</v>
+        <v>1049.869086080857</v>
       </c>
       <c r="D88">
-        <v>1694.813888620432</v>
+        <v>1706.487086080857</v>
       </c>
       <c r="E88">
-        <v>-45.39600000000007</v>
+        <v>-36.98199999999997</v>
       </c>
       <c r="F88">
-        <v>723.6039999999999</v>
+        <v>732.018</v>
       </c>
       <c r="G88">
         <v>75.40000000000001</v>
@@ -8503,28 +8503,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M88">
-        <v>38.71281399999999</v>
+        <v>39.162963</v>
       </c>
       <c r="N88">
-        <v>286.0606553877552</v>
+        <v>285.6105063877552</v>
       </c>
       <c r="O88">
-        <v>85.81819661632655</v>
+        <v>85.68315191632654</v>
       </c>
       <c r="P88">
-        <v>200.2424587714286</v>
+        <v>199.9273544714286</v>
       </c>
       <c r="Q88">
-        <v>324.1424587714286</v>
+        <v>323.8273544714286</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3844398154310375</v>
+        <v>0.4090145480457717</v>
       </c>
       <c r="T88">
-        <v>2.361146659876606</v>
+        <v>2.532492571333544</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>8.389301521396899</v>
+        <v>8.292872768277395</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08575339124595033</v>
+        <v>0.08547820833155539</v>
       </c>
       <c r="C89">
-        <v>1049.869086080857</v>
+        <v>1053.290199345071</v>
       </c>
       <c r="D89">
-        <v>1706.487086080857</v>
+        <v>1718.322199345071</v>
       </c>
       <c r="E89">
-        <v>-36.98199999999997</v>
+        <v>-28.56799999999998</v>
       </c>
       <c r="F89">
-        <v>732.018</v>
+        <v>740.432</v>
       </c>
       <c r="G89">
         <v>75.40000000000001</v>
@@ -8585,28 +8585,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M89">
-        <v>39.162963</v>
+        <v>39.613112</v>
       </c>
       <c r="N89">
-        <v>285.6105063877552</v>
+        <v>285.1603573877551</v>
       </c>
       <c r="O89">
-        <v>85.68315191632654</v>
+        <v>85.54810721632654</v>
       </c>
       <c r="P89">
-        <v>199.9273544714286</v>
+        <v>199.6122501714286</v>
       </c>
       <c r="Q89">
-        <v>323.8273544714286</v>
+        <v>323.5122501714286</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4090145480457717</v>
+        <v>0.4376850694296284</v>
       </c>
       <c r="T89">
-        <v>2.532492571333544</v>
+        <v>2.732396134699973</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>8.292872768277395</v>
+        <v>8.198635577728787</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08547820833155539</v>
+        <v>0.08520302541716046</v>
       </c>
       <c r="C90">
-        <v>1053.290199345071</v>
+        <v>1056.876620776654</v>
       </c>
       <c r="D90">
-        <v>1718.322199345071</v>
+        <v>1730.322620776654</v>
       </c>
       <c r="E90">
-        <v>-28.56799999999998</v>
+        <v>-20.154</v>
       </c>
       <c r="F90">
-        <v>740.432</v>
+        <v>748.846</v>
       </c>
       <c r="G90">
         <v>75.40000000000001</v>
@@ -8667,28 +8667,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M90">
-        <v>39.613112</v>
+        <v>40.063261</v>
       </c>
       <c r="N90">
-        <v>285.1603573877551</v>
+        <v>284.7102083877551</v>
       </c>
       <c r="O90">
-        <v>85.54810721632654</v>
+        <v>85.41306251632653</v>
       </c>
       <c r="P90">
-        <v>199.6122501714286</v>
+        <v>199.2971458714286</v>
       </c>
       <c r="Q90">
-        <v>323.5122501714286</v>
+        <v>323.1971458714286</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4376850694296284</v>
+        <v>0.4715684128832771</v>
       </c>
       <c r="T90">
-        <v>2.732396134699973</v>
+        <v>2.96864580049666</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>8.198635577728787</v>
+        <v>8.10651607685543</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08520302541716046</v>
+        <v>0.08492784250276554</v>
       </c>
       <c r="C91">
-        <v>1056.876620776654</v>
+        <v>1060.631838172045</v>
       </c>
       <c r="D91">
-        <v>1730.322620776654</v>
+        <v>1742.491838172045</v>
       </c>
       <c r="E91">
-        <v>-20.154</v>
+        <v>-11.74000000000001</v>
       </c>
       <c r="F91">
-        <v>748.846</v>
+        <v>757.26</v>
       </c>
       <c r="G91">
         <v>75.40000000000001</v>
@@ -8749,28 +8749,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M91">
-        <v>40.063261</v>
+        <v>40.51341</v>
       </c>
       <c r="N91">
-        <v>284.7102083877551</v>
+        <v>284.2600593877551</v>
       </c>
       <c r="O91">
-        <v>85.41306251632653</v>
+        <v>85.27801781632654</v>
       </c>
       <c r="P91">
-        <v>199.2971458714286</v>
+        <v>198.9820415714286</v>
       </c>
       <c r="Q91">
-        <v>323.1971458714286</v>
+        <v>322.8820415714285</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4715684128832771</v>
+        <v>0.5122284250276555</v>
       </c>
       <c r="T91">
-        <v>2.96864580049666</v>
+        <v>3.252145399452685</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>8.10651607685543</v>
+        <v>8.016443676001479</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08492784250276554</v>
+        <v>0.08465265958837061</v>
       </c>
       <c r="C92">
-        <v>1060.631838172045</v>
+        <v>1064.559438140174</v>
       </c>
       <c r="D92">
-        <v>1742.491838172045</v>
+        <v>1754.833438140174</v>
       </c>
       <c r="E92">
-        <v>-11.74000000000001</v>
+        <v>-3.326000000000022</v>
       </c>
       <c r="F92">
-        <v>757.26</v>
+        <v>765.674</v>
       </c>
       <c r="G92">
         <v>75.40000000000001</v>
@@ -8831,28 +8831,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M92">
-        <v>40.51341</v>
+        <v>40.963559</v>
       </c>
       <c r="N92">
-        <v>284.2600593877551</v>
+        <v>283.8099103877552</v>
       </c>
       <c r="O92">
-        <v>85.27801781632654</v>
+        <v>85.14297311632654</v>
       </c>
       <c r="P92">
-        <v>198.9820415714286</v>
+        <v>198.6669372714286</v>
       </c>
       <c r="Q92">
-        <v>322.8820415714285</v>
+        <v>322.5669372714286</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5122284250276555</v>
+        <v>0.5619239954263403</v>
       </c>
       <c r="T92">
-        <v>3.252145399452685</v>
+        <v>3.598644909287827</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>8.016443676001479</v>
+        <v>7.928350888353114</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08465265958837061</v>
+        <v>0.08437747667397569</v>
       </c>
       <c r="C93">
-        <v>1064.559438140174</v>
+        <v>1068.663109626729</v>
       </c>
       <c r="D93">
-        <v>1754.833438140174</v>
+        <v>1767.351109626729</v>
       </c>
       <c r="E93">
-        <v>-3.326000000000022</v>
+        <v>5.087999999999965</v>
       </c>
       <c r="F93">
-        <v>765.674</v>
+        <v>774.088</v>
       </c>
       <c r="G93">
         <v>75.40000000000001</v>
@@ -8913,28 +8913,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M93">
-        <v>40.963559</v>
+        <v>41.413708</v>
       </c>
       <c r="N93">
-        <v>283.8099103877552</v>
+        <v>283.3597613877552</v>
       </c>
       <c r="O93">
-        <v>85.14297311632654</v>
+        <v>85.00792841632655</v>
       </c>
       <c r="P93">
-        <v>198.6669372714286</v>
+        <v>198.3518329714286</v>
       </c>
       <c r="Q93">
-        <v>322.5669372714286</v>
+        <v>322.2518329714286</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5619239954263403</v>
+        <v>0.6240434584246963</v>
       </c>
       <c r="T93">
-        <v>3.598644909287827</v>
+        <v>4.031769296581754</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>7.928350888353114</v>
+        <v>7.842173161305797</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08437747667397569</v>
+        <v>0.08410229375958075</v>
       </c>
       <c r="C94">
-        <v>1068.663109626729</v>
+        <v>1072.946647590354</v>
       </c>
       <c r="D94">
-        <v>1767.351109626729</v>
+        <v>1780.048647590354</v>
       </c>
       <c r="E94">
-        <v>5.087999999999965</v>
+        <v>13.50200000000007</v>
       </c>
       <c r="F94">
-        <v>774.088</v>
+        <v>782.5020000000001</v>
       </c>
       <c r="G94">
         <v>75.40000000000001</v>
@@ -8995,28 +8995,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M94">
-        <v>41.413708</v>
+        <v>41.863857</v>
       </c>
       <c r="N94">
-        <v>283.3597613877552</v>
+        <v>282.9096123877551</v>
       </c>
       <c r="O94">
-        <v>85.00792841632655</v>
+        <v>84.87288371632654</v>
       </c>
       <c r="P94">
-        <v>198.3518329714286</v>
+        <v>198.0367286714286</v>
       </c>
       <c r="Q94">
-        <v>322.2518329714286</v>
+        <v>321.9367286714286</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6240434584246963</v>
+        <v>0.7039113394225827</v>
       </c>
       <c r="T94">
-        <v>4.031769296581754</v>
+        <v>4.588643508816804</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>7.842173161305797</v>
+        <v>7.75784871871111</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08410229375958075</v>
+        <v>0.08382711084518582</v>
       </c>
       <c r="C95">
-        <v>1072.946647590354</v>
+        <v>1077.413956838456</v>
       </c>
       <c r="D95">
-        <v>1780.048647590354</v>
+        <v>1792.929956838456</v>
       </c>
       <c r="E95">
-        <v>13.50200000000007</v>
+        <v>21.91600000000005</v>
       </c>
       <c r="F95">
-        <v>782.5020000000001</v>
+        <v>790.9160000000001</v>
       </c>
       <c r="G95">
         <v>75.40000000000001</v>
@@ -9077,28 +9077,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M95">
-        <v>41.863857</v>
+        <v>42.314006</v>
       </c>
       <c r="N95">
-        <v>282.9096123877551</v>
+        <v>282.4594633877551</v>
       </c>
       <c r="O95">
-        <v>84.87288371632654</v>
+        <v>84.73783901632653</v>
       </c>
       <c r="P95">
-        <v>198.0367286714286</v>
+        <v>197.7216243714286</v>
       </c>
       <c r="Q95">
-        <v>321.9367286714286</v>
+        <v>321.6216243714286</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7039113394225827</v>
+        <v>0.8104018474197646</v>
       </c>
       <c r="T95">
-        <v>4.588643508816804</v>
+        <v>5.331142458463538</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.75784871871111</v>
+        <v>7.675318413192907</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08382711084518582</v>
+        <v>0.08408392793079089</v>
       </c>
       <c r="C96">
-        <v>1077.413956838456</v>
+        <v>1056.972584750574</v>
       </c>
       <c r="D96">
-        <v>1792.929956838456</v>
+        <v>1780.902584750574</v>
       </c>
       <c r="E96">
-        <v>21.91600000000005</v>
+        <v>30.33000000000004</v>
       </c>
       <c r="F96">
-        <v>790.9160000000001</v>
+        <v>799.33</v>
       </c>
       <c r="G96">
         <v>75.40000000000001</v>
@@ -9159,45 +9159,45 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M96">
-        <v>42.314006</v>
+        <v>43.40361900000001</v>
       </c>
       <c r="N96">
-        <v>282.4594633877551</v>
+        <v>281.3698503877552</v>
       </c>
       <c r="O96">
-        <v>84.73783901632653</v>
+        <v>84.41095511632655</v>
       </c>
       <c r="P96">
-        <v>197.7216243714286</v>
+        <v>196.9588952714286</v>
       </c>
       <c r="Q96">
-        <v>321.6216243714286</v>
+        <v>320.8588952714286</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8104018474197646</v>
+        <v>0.9594885586158194</v>
       </c>
       <c r="T96">
-        <v>5.331142458463538</v>
+        <v>6.370640987968966</v>
       </c>
       <c r="U96">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V96">
         <v>0.3</v>
       </c>
       <c r="W96">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y96">
-        <v>7.675318413192907</v>
+        <v>7.482635708044417</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08408392793079089</v>
+        <v>0.08381434501639598</v>
       </c>
       <c r="C97">
-        <v>1056.972584750574</v>
+        <v>1061.188051570097</v>
       </c>
       <c r="D97">
-        <v>1780.902584750574</v>
+        <v>1793.532051570097</v>
       </c>
       <c r="E97">
-        <v>30.33000000000004</v>
+        <v>38.74400000000003</v>
       </c>
       <c r="F97">
-        <v>799.33</v>
+        <v>807.744</v>
       </c>
       <c r="G97">
         <v>75.40000000000001</v>
@@ -9241,28 +9241,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M97">
-        <v>43.40361900000001</v>
+        <v>43.8604992</v>
       </c>
       <c r="N97">
-        <v>281.3698503877552</v>
+        <v>280.9129701877551</v>
       </c>
       <c r="O97">
-        <v>84.41095511632655</v>
+        <v>84.27389105632655</v>
       </c>
       <c r="P97">
-        <v>196.9588952714286</v>
+        <v>196.6390791314286</v>
       </c>
       <c r="Q97">
-        <v>320.8588952714286</v>
+        <v>320.5390791314286</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9594885586158194</v>
+        <v>1.183118625409902</v>
       </c>
       <c r="T97">
-        <v>6.370640987968966</v>
+        <v>7.929888782227109</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>7.482635708044417</v>
+        <v>7.404691586085622</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08381434501639598</v>
+        <v>0.08354476210200106</v>
       </c>
       <c r="C98">
-        <v>1061.188051570098</v>
+        <v>1065.583924267568</v>
       </c>
       <c r="D98">
-        <v>1793.532051570097</v>
+        <v>1806.341924267568</v>
       </c>
       <c r="E98">
-        <v>38.74399999999991</v>
+        <v>47.1579999999999</v>
       </c>
       <c r="F98">
-        <v>807.7439999999999</v>
+        <v>816.1579999999999</v>
       </c>
       <c r="G98">
         <v>75.40000000000001</v>
@@ -9323,28 +9323,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M98">
-        <v>43.8604992</v>
+        <v>44.31737939999999</v>
       </c>
       <c r="N98">
-        <v>280.9129701877551</v>
+        <v>280.4560899877551</v>
       </c>
       <c r="O98">
-        <v>84.27389105632655</v>
+        <v>84.13682699632655</v>
       </c>
       <c r="P98">
-        <v>196.6390791314286</v>
+        <v>196.3192629914286</v>
       </c>
       <c r="Q98">
-        <v>320.5390791314286</v>
+        <v>320.2192629914286</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.183118625409899</v>
+        <v>1.555835403400034</v>
       </c>
       <c r="T98">
-        <v>7.929888782227087</v>
+        <v>10.52863510599065</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.404691586085622</v>
+        <v>7.328354559424946</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08354476210200106</v>
+        <v>0.08327517918760613</v>
       </c>
       <c r="C99">
-        <v>1065.583924267568</v>
+        <v>1070.164096167321</v>
       </c>
       <c r="D99">
-        <v>1806.341924267568</v>
+        <v>1819.336096167321</v>
       </c>
       <c r="E99">
-        <v>47.1579999999999</v>
+        <v>55.572</v>
       </c>
       <c r="F99">
-        <v>816.1579999999999</v>
+        <v>824.572</v>
       </c>
       <c r="G99">
         <v>75.40000000000001</v>
@@ -9405,28 +9405,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M99">
-        <v>44.31737939999999</v>
+        <v>44.7742596</v>
       </c>
       <c r="N99">
-        <v>280.4560899877551</v>
+        <v>279.9992097877551</v>
       </c>
       <c r="O99">
-        <v>84.13682699632655</v>
+        <v>83.99976293632655</v>
       </c>
       <c r="P99">
-        <v>196.3192629914286</v>
+        <v>195.9994468514286</v>
       </c>
       <c r="Q99">
-        <v>320.2192629914286</v>
+        <v>319.8994468514286</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.555835403400034</v>
+        <v>2.301268959380304</v>
       </c>
       <c r="T99">
-        <v>10.52863510599065</v>
+        <v>15.72612775351776</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>7.328354559424946</v>
+        <v>7.253575431267548</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08327517918760613</v>
+        <v>0.08300559627321119</v>
       </c>
       <c r="C100">
-        <v>1070.164096167321</v>
+        <v>1074.932573434104</v>
       </c>
       <c r="D100">
-        <v>1819.336096167321</v>
+        <v>1832.518573434104</v>
       </c>
       <c r="E100">
-        <v>55.572</v>
+        <v>63.98599999999999</v>
       </c>
       <c r="F100">
-        <v>824.572</v>
+        <v>832.986</v>
       </c>
       <c r="G100">
         <v>75.40000000000001</v>
@@ -9487,28 +9487,28 @@
         <v>324.7734693877551</v>
       </c>
       <c r="M100">
-        <v>44.7742596</v>
+        <v>45.2311398</v>
       </c>
       <c r="N100">
-        <v>279.9992097877551</v>
+        <v>279.5423295877551</v>
       </c>
       <c r="O100">
-        <v>83.99976293632655</v>
+        <v>83.86269887632655</v>
       </c>
       <c r="P100">
-        <v>195.9994468514286</v>
+        <v>195.6796307114286</v>
       </c>
       <c r="Q100">
-        <v>319.8994468514286</v>
+        <v>319.5796307114286</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.301268959380304</v>
+        <v>4.537569627321116</v>
       </c>
       <c r="T100">
-        <v>15.72612775351776</v>
+        <v>31.31860569609912</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>7.253575431267548</v>
+        <v>7.180306992567876</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08300559627321119</v>
-      </c>
-      <c r="C101">
-        <v>1074.932573434104</v>
-      </c>
-      <c r="D101">
-        <v>1832.518573434104</v>
-      </c>
-      <c r="E101">
-        <v>63.98599999999999</v>
-      </c>
-      <c r="F101">
-        <v>832.986</v>
-      </c>
-      <c r="G101">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>448.6734693877551</v>
-      </c>
-      <c r="K101">
-        <v>123.9</v>
-      </c>
-      <c r="L101">
-        <v>324.7734693877551</v>
-      </c>
-      <c r="M101">
-        <v>45.2311398</v>
-      </c>
-      <c r="N101">
-        <v>279.5423295877551</v>
-      </c>
-      <c r="O101">
-        <v>83.86269887632655</v>
-      </c>
-      <c r="P101">
-        <v>195.6796307114286</v>
-      </c>
-      <c r="Q101">
-        <v>319.5796307114286</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.537569627321116</v>
-      </c>
-      <c r="T101">
-        <v>31.31860569609912</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03801</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>7.180306992567876</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
